--- a/outputs/58147.xlsx
+++ b/outputs/58147.xlsx
@@ -363,56 +363,60 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -673,665 +677,665 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="18.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="35.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="32.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="14.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="15.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="str">
+      <c r="E2" s="2" t="str">
         <f aca="false">IF(C2="","",C2&amp;", "&amp;D2)</f>
         <v>Tbnor, Cadigan</v>
       </c>
-      <c r="F2" s="0" t="str">
+      <c r="F2" s="2" t="str">
         <f aca="false">IF(C2="","",E2&amp;" - "&amp;B2)</f>
         <v>Tbnor, Cadigan - TA32785655</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="0" t="str">
+      <c r="E3" s="2" t="str">
         <f aca="false">IF(C3="","",C3&amp;", "&amp;D3)</f>
         <v>Abo, Cadiz</v>
       </c>
-      <c r="F3" s="0" t="str">
+      <c r="F3" s="2" t="str">
         <f aca="false">IF(C3="","",E3&amp;" - "&amp;B3)</f>
         <v>Abo, Cadiz - SA12442673</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="0" t="str">
+      <c r="E4" s="2" t="str">
         <f aca="false">IF(C4="","",C4&amp;", "&amp;D4)</f>
         <v>Tbra, Cadle</v>
       </c>
-      <c r="F4" s="0" t="str">
+      <c r="F4" s="2" t="str">
         <f aca="false">IF(C4="","",E4&amp;" - "&amp;B4)</f>
         <v>Tbra, Cadle - AA21259159</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="0" t="str">
+      <c r="E5" s="2" t="str">
         <f aca="false">IF(C5="","",C5&amp;", "&amp;D5)</f>
         <v>Abrahaim, Cadman</v>
       </c>
-      <c r="F5" s="0" t="str">
+      <c r="F5" s="2" t="str">
         <f aca="false">IF(C5="","",E5&amp;" - "&amp;B5)</f>
         <v>Abrahaim, Cadman - CA84636028</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="0" t="str">
+      <c r="E6" s="2" t="str">
         <f aca="false">IF(C6="","",C6&amp;", "&amp;D6)</f>
         <v>Abraham, Cadmus</v>
       </c>
-      <c r="F6" s="0" t="str">
+      <c r="F6" s="2" t="str">
         <f aca="false">IF(C6="","",E6&amp;" - "&amp;B6)</f>
         <v>Abraham, Cadmus - OA61505754</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="0" t="str">
+      <c r="E7" s="2" t="str">
         <f aca="false">IF(C7="","",C7&amp;", "&amp;D7)</f>
         <v>Tbrahame, Cadogan</v>
       </c>
-      <c r="F7" s="0" t="str">
+      <c r="F7" s="2" t="str">
         <f aca="false">IF(C7="","",E7&amp;" - "&amp;B7)</f>
         <v>Tbrahame, Cadogan - LB71531251</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="0" t="str">
+      <c r="E8" s="2" t="str">
         <f aca="false">IF(C8="","",C8&amp;", "&amp;D8)</f>
         <v>Abrahamo, Cadoret</v>
       </c>
-      <c r="F8" s="0" t="str">
+      <c r="F8" s="2" t="str">
         <f aca="false">IF(C8="","",E8&amp;" - "&amp;B8)</f>
         <v>Abrahamo, Cadoret - TB19548089</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="0" t="str">
+      <c r="E9" s="2" t="str">
         <f aca="false">IF(C9="","",C9&amp;", "&amp;D9)</f>
         <v>Abrahan, Cadorette</v>
       </c>
-      <c r="F9" s="0" t="str">
+      <c r="F9" s="2" t="str">
         <f aca="false">IF(C9="","",E9&amp;" - "&amp;B9)</f>
         <v>Abrahan, Cadorette - SB46327164</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="0" t="str">
+      <c r="E10" s="2" t="str">
         <f aca="false">IF(C10="","",C10&amp;", "&amp;D10)</f>
         <v>Abraheem, Cadotte</v>
       </c>
-      <c r="F10" s="0" t="str">
+      <c r="F10" s="2" t="str">
         <f aca="false">IF(C10="","",E10&amp;" - "&amp;B10)</f>
         <v>Abraheem, Cadotte - PB67349700</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="0" t="str">
+      <c r="E11" s="2" t="str">
         <f aca="false">IF(C11="","",C11&amp;", "&amp;D11)</f>
         <v>Tbrahem, Cadwalader</v>
       </c>
-      <c r="F11" s="0" t="str">
+      <c r="F11" s="2" t="str">
         <f aca="false">IF(C11="","",E11&amp;" - "&amp;B11)</f>
         <v>Tbrahem, Cadwalader - EB32531079</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="0" t="str">
+      <c r="E12" s="2" t="str">
         <f aca="false">IF(C12="","",C12&amp;", "&amp;D12)</f>
         <v>Abrahim, Cadwallader</v>
       </c>
-      <c r="F12" s="0" t="str">
+      <c r="F12" s="2" t="str">
         <f aca="false">IF(C12="","",E12&amp;" - "&amp;B12)</f>
         <v>Abrahim, Cadwallader - SC17296774</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="0" t="str">
+      <c r="E13" s="2" t="str">
         <f aca="false">IF(C13="","",C13&amp;", "&amp;D13)</f>
         <v>Abrahm, Cadwell</v>
       </c>
-      <c r="F13" s="0" t="str">
+      <c r="F13" s="2" t="str">
         <f aca="false">IF(C13="","",E13&amp;" - "&amp;B13)</f>
         <v>Abrahm, Cadwell - FC70634829</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="0" t="str">
+      <c r="E14" s="2" t="str">
         <f aca="false">IF(C14="","",C14&amp;", "&amp;D14)</f>
         <v>Abrahon, Cady</v>
       </c>
-      <c r="F14" s="0" t="str">
+      <c r="F14" s="2" t="str">
         <f aca="false">IF(C14="","",E14&amp;" - "&amp;B14)</f>
         <v>Abrahon, Cady - AD17153037</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="0" t="str">
+      <c r="E15" s="2" t="str">
         <f aca="false">IF(C15="","",C15&amp;", "&amp;D15)</f>
         <v>Abrahsa, Caesar</v>
       </c>
-      <c r="F15" s="0" t="str">
+      <c r="F15" s="2" t="str">
         <f aca="false">IF(C15="","",E15&amp;" - "&amp;B15)</f>
         <v>Abrahsa, Caesar - CD14845828</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="0" t="str">
+      <c r="E16" s="2" t="str">
         <f aca="false">IF(C16="","",C16&amp;", "&amp;D16)</f>
         <v>Abram, Caetano</v>
       </c>
-      <c r="F16" s="0" t="str">
+      <c r="F16" s="2" t="str">
         <f aca="false">IF(C16="","",E16&amp;" - "&amp;B16)</f>
         <v>Abram, Caetano - JG66805710</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="0" t="str">
+      <c r="E17" s="2" t="str">
         <f aca="false">IF(C17="","",C17&amp;", "&amp;D17)</f>
         <v>Abramo, Cafarella</v>
       </c>
-      <c r="F17" s="0" t="str">
+      <c r="F17" s="2" t="str">
         <f aca="false">IF(C17="","",E17&amp;" - "&amp;B17)</f>
         <v>Abramo, Cafarella - CH36848865</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="0" t="str">
+      <c r="E18" s="2" t="str">
         <f aca="false">IF(C18="","",C18&amp;", "&amp;D18)</f>
         <v>Absalon, Cafarelli</v>
       </c>
-      <c r="F18" s="0" t="str">
+      <c r="F18" s="2" t="str">
         <f aca="false">IF(C18="","",E18&amp;" - "&amp;B18)</f>
         <v>Absalon, Cafarelli - CL41033165</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="0" t="str">
+      <c r="E19" s="2" t="str">
         <f aca="false">IF(C19="","",C19&amp;", "&amp;D19)</f>
         <v>Abselon, Cafaro</v>
       </c>
-      <c r="F19" s="0" t="str">
+      <c r="F19" s="2" t="str">
         <f aca="false">IF(C19="","",E19&amp;" - "&amp;B19)</f>
         <v>Abselon, Cafaro - LL21590248</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="0" t="str">
+      <c r="E20" s="2" t="str">
         <f aca="false">IF(C20="","",C20&amp;", "&amp;D20)</f>
         <v>Absolom, Cafasso</v>
       </c>
-      <c r="F20" s="0" t="str">
+      <c r="F20" s="2" t="str">
         <f aca="false">IF(C20="","",E20&amp;" - "&amp;B20)</f>
         <v>Absolom, Cafasso - RK32756907</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="0" t="str">
+      <c r="E21" s="2" t="str">
         <f aca="false">IF(C21="","",C21&amp;", "&amp;D21)</f>
         <v>Absolum, Caggiano</v>
       </c>
-      <c r="F21" s="0" t="str">
+      <c r="F21" s="2" t="str">
         <f aca="false">IF(C21="","",E21&amp;" - "&amp;B21)</f>
         <v>Absolum, Caggiano - EM26000697</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="0" t="str">
+      <c r="E22" s="2" t="str">
         <f aca="false">IF(C22="","",C22&amp;", "&amp;D22)</f>
         <v>Tbnor, Cadigan</v>
       </c>
-      <c r="F22" s="0" t="str">
+      <c r="F22" s="2" t="str">
         <f aca="false">IF(C22="","",E22&amp;" - "&amp;B22)</f>
         <v>Tbnor, Cadigan - MM12168514</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="0" t="str">
+      <c r="E23" s="2" t="str">
         <f aca="false">IF(C23="","",C23&amp;", "&amp;D23)</f>
         <v/>
       </c>
-      <c r="F23" s="0" t="str">
+      <c r="F23" s="2" t="str">
         <f aca="false">IF(C23="","",E23&amp;" - "&amp;B23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="0" t="str">
+      <c r="E24" s="2" t="str">
         <f aca="false">IF(C24="","",C24&amp;", "&amp;D24)</f>
         <v/>
       </c>
-      <c r="F24" s="0" t="str">
+      <c r="F24" s="2" t="str">
         <f aca="false">IF(C24="","",E24&amp;" - "&amp;B24)</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E25" s="0" t="str">
+      <c r="E25" s="2" t="str">
         <f aca="false">IF(C25="","",C25&amp;", "&amp;D25)</f>
         <v/>
       </c>
-      <c r="F25" s="0" t="str">
+      <c r="F25" s="2" t="str">
         <f aca="false">IF(C25="","",E25&amp;" - "&amp;B25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="0" t="str">
+      <c r="E26" s="2" t="str">
         <f aca="false">IF(C26="","",C26&amp;", "&amp;D26)</f>
         <v/>
       </c>
-      <c r="F26" s="0" t="str">
+      <c r="F26" s="2" t="str">
         <f aca="false">IF(C26="","",E26&amp;" - "&amp;B26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="0" t="str">
+      <c r="E27" s="2" t="str">
         <f aca="false">IF(C27="","",C27&amp;", "&amp;D27)</f>
         <v/>
       </c>
-      <c r="F27" s="0" t="str">
+      <c r="F27" s="2" t="str">
         <f aca="false">IF(C27="","",E27&amp;" - "&amp;B27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5"/>
-      <c r="E28" s="0" t="str">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6"/>
+      <c r="E28" s="2" t="str">
         <f aca="false">IF(C28="","",C28&amp;", "&amp;D28)</f>
         <v/>
       </c>
-      <c r="F28" s="0" t="str">
+      <c r="F28" s="2" t="str">
         <f aca="false">IF(C28="","",E28&amp;" - "&amp;B28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5"/>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1353,114 +1357,114 @@
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="5" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="0" width="13.16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="0" width="14.5"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="0" width="23.16"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="0" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="0" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="5" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="36.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="32.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="6" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="2" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="2" width="14.5"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="2" width="23.16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="2" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="2" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="6" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="36.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="32.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="14.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <f aca="false">IF(Sheet1!A2="","",Sheet1!A2)</f>
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="6" t="str">
         <f aca="false">IF(Sheet1!B2="","",Sheet1!B2)</f>
         <v>TA32785655</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="6" t="str">
         <f aca="false">IF(Sheet1!C2="","",Sheet1!C2)</f>
         <v>Tbnor</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="6" t="str">
         <f aca="false">IF(Sheet1!D2="","",Sheet1!D2)</f>
         <v>Cadigan</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="6" t="str">
         <f aca="false">IF(Sheet1!E2="","",Sheet1!E2)</f>
         <v>Tbnor, Cadigan</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="6" t="str">
         <f aca="false">IF(Sheet1!F2="","",Sheet1!F2)</f>
         <v>Tbnor, Cadigan - TA32785655</v>
       </c>
-      <c r="G2" s="8" t="str">
+      <c r="G2" s="9" t="str">
         <f aca="false">LEFT(F2,1)</f>
         <v>T</v>
       </c>
-      <c r="H2" s="9" t="str">
+      <c r="H2" s="10" t="str">
         <f aca="false">1&amp;" - "&amp;C2</f>
         <v>1 - Tbnor</v>
       </c>
-      <c r="I2" s="10" t="str">
+      <c r="I2" s="11" t="str">
         <f aca="false">1&amp;" - "&amp;F2</f>
         <v>1 - Tbnor, Cadigan - TA32785655</v>
       </c>
-      <c r="J2" s="11" t="str">
-        <f aca="false">IFERROR(MID(I2,FIND(" - ",I2)+3,FIND(" - ",I2,FIND(" - ",I2)+1)-FIND(" - ",I2)-3),LEFT(I2,FIND(" - ",I2)-1))</f>
+      <c r="J2" s="12" t="str">
+        <f aca="false">IF(LEN(I2)-LEN(SUBSTITUTE(I2," - ",""))&gt;=6,MID(I2,SEARCH(" - ",I2)+3,SEARCH(" - ",I2,SEARCH(" - ",I2)+1)-SEARCH(" - ",I2)-3),LEFT(I2,SEARCH(" - ",I2)-1))</f>
         <v>Tbnor, Cadigan</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <f aca="false">IF(Sheet1!A3="","",Sheet1!A3)</f>
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="str">
+      <c r="B3" s="6" t="str">
         <f aca="false">IF(Sheet1!B3="","",Sheet1!B3)</f>
         <v>SA12442673</v>
       </c>
-      <c r="C3" s="5" t="str">
+      <c r="C3" s="6" t="str">
         <f aca="false">IF(Sheet1!C3="","",Sheet1!C3)</f>
         <v>Abo</v>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="6" t="str">
         <f aca="false">IF(Sheet1!D3="","",Sheet1!D3)</f>
         <v>Cadiz</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="6" t="str">
         <f aca="false">IF(Sheet1!E3="","",Sheet1!E3)</f>
         <v>Abo, Cadiz</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="6" t="str">
         <f aca="false">IF(Sheet1!F3="","",Sheet1!F3)</f>
         <v>Abo, Cadiz - SA12442673</v>
       </c>
@@ -1468,81 +1472,81 @@
         <f aca="false">LEFT(F3,1)</f>
         <v>A</v>
       </c>
-      <c r="H3" s="5" t="str">
+      <c r="H3" s="6" t="str">
         <f aca="false">C4</f>
         <v>Tbra</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="11" t="str">
-        <f aca="false">IFERROR(MID(I3,FIND(" - ",I3)+3,FIND(" - ",I3,FIND(" - ",I3)+1)-FIND(" - ",I3)-3),LEFT(I3,FIND(" - ",I3)-1))</f>
+      <c r="J3" s="12" t="str">
+        <f aca="false">IF(LEN(I3)-LEN(SUBSTITUTE(I3," - ",""))&gt;=6,MID(I3,SEARCH(" - ",I3)+3,SEARCH(" - ",I3,SEARCH(" - ",I3)+1)-SEARCH(" - ",I3)-3),LEFT(I3,SEARCH(" - ",I3)-1))</f>
         <v>Tbra, Cadle</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <f aca="false">IF(Sheet1!A4="","",Sheet1!A4)</f>
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="str">
+      <c r="B4" s="6" t="str">
         <f aca="false">IF(Sheet1!B4="","",Sheet1!B4)</f>
         <v>AA21259159</v>
       </c>
-      <c r="C4" s="5" t="str">
+      <c r="C4" s="6" t="str">
         <f aca="false">IF(Sheet1!C4="","",Sheet1!C4)</f>
         <v>Tbra</v>
       </c>
-      <c r="D4" s="5" t="str">
+      <c r="D4" s="6" t="str">
         <f aca="false">IF(Sheet1!D4="","",Sheet1!D4)</f>
         <v>Cadle</v>
       </c>
-      <c r="E4" s="5" t="str">
+      <c r="E4" s="6" t="str">
         <f aca="false">IF(Sheet1!E4="","",Sheet1!E4)</f>
         <v>Tbra, Cadle</v>
       </c>
-      <c r="F4" s="5" t="str">
+      <c r="F4" s="6" t="str">
         <f aca="false">IF(Sheet1!F4="","",Sheet1!F4)</f>
         <v>Tbra, Cadle - AA21259159</v>
       </c>
-      <c r="G4" s="8" t="str">
+      <c r="G4" s="9" t="str">
         <f aca="false">LEFT(F4,1)</f>
         <v>T</v>
       </c>
-      <c r="H4" s="9" t="str">
+      <c r="H4" s="10" t="str">
         <f aca="false">C7</f>
         <v>Tbrahame</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="11" t="str">
-        <f aca="false">IFERROR(MID(I4,FIND(" - ",I4)+3,FIND(" - ",I4,FIND(" - ",I4)+1)-FIND(" - ",I4)-3),LEFT(I4,FIND(" - ",I4)-1))</f>
+      <c r="J4" s="12" t="str">
+        <f aca="false">IF(LEN(I4)-LEN(SUBSTITUTE(I4," - ",""))&gt;=6,MID(I4,SEARCH(" - ",I4)+3,SEARCH(" - ",I4,SEARCH(" - ",I4)+1)-SEARCH(" - ",I4)-3),LEFT(I4,SEARCH(" - ",I4)-1))</f>
         <v>Tbrahame, Cadogan</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <f aca="false">IF(Sheet1!A5="","",Sheet1!A5)</f>
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="6" t="str">
         <f aca="false">IF(Sheet1!B5="","",Sheet1!B5)</f>
         <v>CA84636028</v>
       </c>
-      <c r="C5" s="5" t="str">
+      <c r="C5" s="6" t="str">
         <f aca="false">IF(Sheet1!C5="","",Sheet1!C5)</f>
         <v>Abrahaim</v>
       </c>
-      <c r="D5" s="5" t="str">
+      <c r="D5" s="6" t="str">
         <f aca="false">IF(Sheet1!D5="","",Sheet1!D5)</f>
         <v>Cadman</v>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="E5" s="6" t="str">
         <f aca="false">IF(Sheet1!E5="","",Sheet1!E5)</f>
         <v>Abrahaim, Cadman</v>
       </c>
-      <c r="F5" s="5" t="str">
+      <c r="F5" s="6" t="str">
         <f aca="false">IF(Sheet1!F5="","",Sheet1!F5)</f>
         <v>Abrahaim, Cadman - CA84636028</v>
       </c>
@@ -1550,40 +1554,40 @@
         <f aca="false">LEFT(F5,1)</f>
         <v>A</v>
       </c>
-      <c r="H5" s="5" t="str">
+      <c r="H5" s="6" t="str">
         <f aca="false">C11</f>
         <v>Tbrahem</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="11" t="str">
-        <f aca="false">IFERROR(MID(I5,FIND(" - ",I5)+3,FIND(" - ",I5,FIND(" - ",I5)+1)-FIND(" - ",I5)-3),LEFT(I5,FIND(" - ",I5)-1))</f>
+      <c r="J5" s="12" t="str">
+        <f aca="false">IF(LEN(I5)-LEN(SUBSTITUTE(I5," - ",""))&gt;=6,MID(I5,SEARCH(" - ",I5)+3,SEARCH(" - ",I5,SEARCH(" - ",I5)+1)-SEARCH(" - ",I5)-3),LEFT(I5,SEARCH(" - ",I5)-1))</f>
         <v>Tbrahem, Cadwalader</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <f aca="false">IF(Sheet1!A6="","",Sheet1!A6)</f>
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="str">
+      <c r="B6" s="6" t="str">
         <f aca="false">IF(Sheet1!B6="","",Sheet1!B6)</f>
         <v>OA61505754</v>
       </c>
-      <c r="C6" s="5" t="str">
+      <c r="C6" s="6" t="str">
         <f aca="false">IF(Sheet1!C6="","",Sheet1!C6)</f>
         <v>Abraham</v>
       </c>
-      <c r="D6" s="5" t="str">
+      <c r="D6" s="6" t="str">
         <f aca="false">IF(Sheet1!D6="","",Sheet1!D6)</f>
         <v>Cadmus</v>
       </c>
-      <c r="E6" s="5" t="str">
+      <c r="E6" s="6" t="str">
         <f aca="false">IF(Sheet1!E6="","",Sheet1!E6)</f>
         <v>Abraham, Cadmus</v>
       </c>
-      <c r="F6" s="5" t="str">
+      <c r="F6" s="6" t="str">
         <f aca="false">IF(Sheet1!F6="","",Sheet1!F6)</f>
         <v>Abraham, Cadmus - OA61505754</v>
       </c>
@@ -1591,73 +1595,73 @@
         <f aca="false">LEFT(F6,1)</f>
         <v>A</v>
       </c>
-      <c r="H6" s="5" t="str">
+      <c r="H6" s="6" t="str">
         <f aca="false">2&amp;" - "&amp;C22</f>
         <v>2 - Tbnor</v>
       </c>
-      <c r="I6" s="10" t="str">
+      <c r="I6" s="11" t="str">
         <f aca="false">2&amp;" - "&amp;F22</f>
         <v>2 - Tbnor, Cadigan - MM12168514</v>
       </c>
-      <c r="J6" s="11" t="str">
-        <f aca="false">IFERROR(MID(I6,FIND(" - ",I6)+3,FIND(" - ",I6,FIND(" - ",I6)+1)-FIND(" - ",I6)-3),LEFT(I6,FIND(" - ",I6)-1))</f>
+      <c r="J6" s="12" t="str">
+        <f aca="false">IF(LEN(I6)-LEN(SUBSTITUTE(I6," - ",""))&gt;=6,MID(I6,SEARCH(" - ",I6)+3,SEARCH(" - ",I6,SEARCH(" - ",I6)+1)-SEARCH(" - ",I6)-3),LEFT(I6,SEARCH(" - ",I6)-1))</f>
         <v>Tbnor, Cadigan</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <f aca="false">IF(Sheet1!A7="","",Sheet1!A7)</f>
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="str">
+      <c r="B7" s="6" t="str">
         <f aca="false">IF(Sheet1!B7="","",Sheet1!B7)</f>
         <v>LB71531251</v>
       </c>
-      <c r="C7" s="5" t="str">
+      <c r="C7" s="6" t="str">
         <f aca="false">IF(Sheet1!C7="","",Sheet1!C7)</f>
         <v>Tbrahame</v>
       </c>
-      <c r="D7" s="5" t="str">
+      <c r="D7" s="6" t="str">
         <f aca="false">IF(Sheet1!D7="","",Sheet1!D7)</f>
         <v>Cadogan</v>
       </c>
-      <c r="E7" s="5" t="str">
+      <c r="E7" s="6" t="str">
         <f aca="false">IF(Sheet1!E7="","",Sheet1!E7)</f>
         <v>Tbrahame, Cadogan</v>
       </c>
-      <c r="F7" s="5" t="str">
+      <c r="F7" s="6" t="str">
         <f aca="false">IF(Sheet1!F7="","",Sheet1!F7)</f>
         <v>Tbrahame, Cadogan - LB71531251</v>
       </c>
-      <c r="G7" s="8" t="str">
+      <c r="G7" s="9" t="str">
         <f aca="false">LEFT(F7,1)</f>
         <v>T</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="10"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <f aca="false">IF(Sheet1!A8="","",Sheet1!A8)</f>
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="str">
+      <c r="B8" s="6" t="str">
         <f aca="false">IF(Sheet1!B8="","",Sheet1!B8)</f>
         <v>TB19548089</v>
       </c>
-      <c r="C8" s="5" t="str">
+      <c r="C8" s="6" t="str">
         <f aca="false">IF(Sheet1!C8="","",Sheet1!C8)</f>
         <v>Abrahamo</v>
       </c>
-      <c r="D8" s="5" t="str">
+      <c r="D8" s="6" t="str">
         <f aca="false">IF(Sheet1!D8="","",Sheet1!D8)</f>
         <v>Cadoret</v>
       </c>
-      <c r="E8" s="5" t="str">
+      <c r="E8" s="6" t="str">
         <f aca="false">IF(Sheet1!E8="","",Sheet1!E8)</f>
         <v>Abrahamo, Cadoret</v>
       </c>
-      <c r="F8" s="5" t="str">
+      <c r="F8" s="6" t="str">
         <f aca="false">IF(Sheet1!F8="","",Sheet1!F8)</f>
         <v>Abrahamo, Cadoret - TB19548089</v>
       </c>
@@ -1665,30 +1669,30 @@
         <f aca="false">LEFT(F8,1)</f>
         <v>A</v>
       </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <f aca="false">IF(Sheet1!A9="","",Sheet1!A9)</f>
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="str">
+      <c r="B9" s="6" t="str">
         <f aca="false">IF(Sheet1!B9="","",Sheet1!B9)</f>
         <v>SB46327164</v>
       </c>
-      <c r="C9" s="5" t="str">
+      <c r="C9" s="6" t="str">
         <f aca="false">IF(Sheet1!C9="","",Sheet1!C9)</f>
         <v>Abrahan</v>
       </c>
-      <c r="D9" s="5" t="str">
+      <c r="D9" s="6" t="str">
         <f aca="false">IF(Sheet1!D9="","",Sheet1!D9)</f>
         <v>Cadorette</v>
       </c>
-      <c r="E9" s="5" t="str">
+      <c r="E9" s="6" t="str">
         <f aca="false">IF(Sheet1!E9="","",Sheet1!E9)</f>
         <v>Abrahan, Cadorette</v>
       </c>
-      <c r="F9" s="5" t="str">
+      <c r="F9" s="6" t="str">
         <f aca="false">IF(Sheet1!F9="","",Sheet1!F9)</f>
         <v>Abrahan, Cadorette - SB46327164</v>
       </c>
@@ -1696,30 +1700,30 @@
         <f aca="false">LEFT(F9,1)</f>
         <v>A</v>
       </c>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <f aca="false">IF(Sheet1!A10="","",Sheet1!A10)</f>
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="str">
+      <c r="B10" s="6" t="str">
         <f aca="false">IF(Sheet1!B10="","",Sheet1!B10)</f>
         <v>PB67349700</v>
       </c>
-      <c r="C10" s="5" t="str">
+      <c r="C10" s="6" t="str">
         <f aca="false">IF(Sheet1!C10="","",Sheet1!C10)</f>
         <v>Abraheem</v>
       </c>
-      <c r="D10" s="5" t="str">
+      <c r="D10" s="6" t="str">
         <f aca="false">IF(Sheet1!D10="","",Sheet1!D10)</f>
         <v>Cadotte</v>
       </c>
-      <c r="E10" s="5" t="str">
+      <c r="E10" s="6" t="str">
         <f aca="false">IF(Sheet1!E10="","",Sheet1!E10)</f>
         <v>Abraheem, Cadotte</v>
       </c>
-      <c r="F10" s="5" t="str">
+      <c r="F10" s="6" t="str">
         <f aca="false">IF(Sheet1!F10="","",Sheet1!F10)</f>
         <v>Abraheem, Cadotte - PB67349700</v>
       </c>
@@ -1727,62 +1731,62 @@
         <f aca="false">LEFT(F10,1)</f>
         <v>A</v>
       </c>
-      <c r="I10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <f aca="false">IF(Sheet1!A11="","",Sheet1!A11)</f>
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="str">
+      <c r="B11" s="6" t="str">
         <f aca="false">IF(Sheet1!B11="","",Sheet1!B11)</f>
         <v>EB32531079</v>
       </c>
-      <c r="C11" s="5" t="str">
+      <c r="C11" s="6" t="str">
         <f aca="false">IF(Sheet1!C11="","",Sheet1!C11)</f>
         <v>Tbrahem</v>
       </c>
-      <c r="D11" s="5" t="str">
+      <c r="D11" s="6" t="str">
         <f aca="false">IF(Sheet1!D11="","",Sheet1!D11)</f>
         <v>Cadwalader</v>
       </c>
-      <c r="E11" s="5" t="str">
+      <c r="E11" s="6" t="str">
         <f aca="false">IF(Sheet1!E11="","",Sheet1!E11)</f>
         <v>Tbrahem, Cadwalader</v>
       </c>
-      <c r="F11" s="5" t="str">
+      <c r="F11" s="6" t="str">
         <f aca="false">IF(Sheet1!F11="","",Sheet1!F11)</f>
         <v>Tbrahem, Cadwalader - EB32531079</v>
       </c>
-      <c r="G11" s="8" t="str">
+      <c r="G11" s="9" t="str">
         <f aca="false">LEFT(F11,1)</f>
         <v>T</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="10"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <f aca="false">IF(Sheet1!A12="","",Sheet1!A12)</f>
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="str">
+      <c r="B12" s="6" t="str">
         <f aca="false">IF(Sheet1!B12="","",Sheet1!B12)</f>
         <v>SC17296774</v>
       </c>
-      <c r="C12" s="5" t="str">
+      <c r="C12" s="6" t="str">
         <f aca="false">IF(Sheet1!C12="","",Sheet1!C12)</f>
         <v>Abrahim</v>
       </c>
-      <c r="D12" s="5" t="str">
+      <c r="D12" s="6" t="str">
         <f aca="false">IF(Sheet1!D12="","",Sheet1!D12)</f>
         <v>Cadwallader</v>
       </c>
-      <c r="E12" s="5" t="str">
+      <c r="E12" s="6" t="str">
         <f aca="false">IF(Sheet1!E12="","",Sheet1!E12)</f>
         <v>Abrahim, Cadwallader</v>
       </c>
-      <c r="F12" s="5" t="str">
+      <c r="F12" s="6" t="str">
         <f aca="false">IF(Sheet1!F12="","",Sheet1!F12)</f>
         <v>Abrahim, Cadwallader - SC17296774</v>
       </c>
@@ -1790,30 +1794,30 @@
         <f aca="false">LEFT(F12,1)</f>
         <v>A</v>
       </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <f aca="false">IF(Sheet1!A13="","",Sheet1!A13)</f>
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="str">
+      <c r="B13" s="6" t="str">
         <f aca="false">IF(Sheet1!B13="","",Sheet1!B13)</f>
         <v>FC70634829</v>
       </c>
-      <c r="C13" s="5" t="str">
+      <c r="C13" s="6" t="str">
         <f aca="false">IF(Sheet1!C13="","",Sheet1!C13)</f>
         <v>Abrahm</v>
       </c>
-      <c r="D13" s="5" t="str">
+      <c r="D13" s="6" t="str">
         <f aca="false">IF(Sheet1!D13="","",Sheet1!D13)</f>
         <v>Cadwell</v>
       </c>
-      <c r="E13" s="5" t="str">
+      <c r="E13" s="6" t="str">
         <f aca="false">IF(Sheet1!E13="","",Sheet1!E13)</f>
         <v>Abrahm, Cadwell</v>
       </c>
-      <c r="F13" s="5" t="str">
+      <c r="F13" s="6" t="str">
         <f aca="false">IF(Sheet1!F13="","",Sheet1!F13)</f>
         <v>Abrahm, Cadwell - FC70634829</v>
       </c>
@@ -1821,30 +1825,30 @@
         <f aca="false">LEFT(F13,1)</f>
         <v>A</v>
       </c>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <f aca="false">IF(Sheet1!A14="","",Sheet1!A14)</f>
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="str">
+      <c r="B14" s="6" t="str">
         <f aca="false">IF(Sheet1!B14="","",Sheet1!B14)</f>
         <v>AD17153037</v>
       </c>
-      <c r="C14" s="5" t="str">
+      <c r="C14" s="6" t="str">
         <f aca="false">IF(Sheet1!C14="","",Sheet1!C14)</f>
         <v>Abrahon</v>
       </c>
-      <c r="D14" s="5" t="str">
+      <c r="D14" s="6" t="str">
         <f aca="false">IF(Sheet1!D14="","",Sheet1!D14)</f>
         <v>Cady</v>
       </c>
-      <c r="E14" s="5" t="str">
+      <c r="E14" s="6" t="str">
         <f aca="false">IF(Sheet1!E14="","",Sheet1!E14)</f>
         <v>Abrahon, Cady</v>
       </c>
-      <c r="F14" s="5" t="str">
+      <c r="F14" s="6" t="str">
         <f aca="false">IF(Sheet1!F14="","",Sheet1!F14)</f>
         <v>Abrahon, Cady - AD17153037</v>
       </c>
@@ -1852,30 +1856,30 @@
         <f aca="false">LEFT(F14,1)</f>
         <v>A</v>
       </c>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <f aca="false">IF(Sheet1!A15="","",Sheet1!A15)</f>
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="str">
+      <c r="B15" s="6" t="str">
         <f aca="false">IF(Sheet1!B15="","",Sheet1!B15)</f>
         <v>CD14845828</v>
       </c>
-      <c r="C15" s="5" t="str">
+      <c r="C15" s="6" t="str">
         <f aca="false">IF(Sheet1!C15="","",Sheet1!C15)</f>
         <v>Abrahsa</v>
       </c>
-      <c r="D15" s="5" t="str">
+      <c r="D15" s="6" t="str">
         <f aca="false">IF(Sheet1!D15="","",Sheet1!D15)</f>
         <v>Caesar</v>
       </c>
-      <c r="E15" s="5" t="str">
+      <c r="E15" s="6" t="str">
         <f aca="false">IF(Sheet1!E15="","",Sheet1!E15)</f>
         <v>Abrahsa, Caesar</v>
       </c>
-      <c r="F15" s="5" t="str">
+      <c r="F15" s="6" t="str">
         <f aca="false">IF(Sheet1!F15="","",Sheet1!F15)</f>
         <v>Abrahsa, Caesar - CD14845828</v>
       </c>
@@ -1883,30 +1887,30 @@
         <f aca="false">LEFT(F15,1)</f>
         <v>A</v>
       </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <f aca="false">IF(Sheet1!A16="","",Sheet1!A16)</f>
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="str">
+      <c r="B16" s="6" t="str">
         <f aca="false">IF(Sheet1!B16="","",Sheet1!B16)</f>
         <v>JG66805710</v>
       </c>
-      <c r="C16" s="5" t="str">
+      <c r="C16" s="6" t="str">
         <f aca="false">IF(Sheet1!C16="","",Sheet1!C16)</f>
         <v>Abram</v>
       </c>
-      <c r="D16" s="5" t="str">
+      <c r="D16" s="6" t="str">
         <f aca="false">IF(Sheet1!D16="","",Sheet1!D16)</f>
         <v>Caetano</v>
       </c>
-      <c r="E16" s="5" t="str">
+      <c r="E16" s="6" t="str">
         <f aca="false">IF(Sheet1!E16="","",Sheet1!E16)</f>
         <v>Abram, Caetano</v>
       </c>
-      <c r="F16" s="5" t="str">
+      <c r="F16" s="6" t="str">
         <f aca="false">IF(Sheet1!F16="","",Sheet1!F16)</f>
         <v>Abram, Caetano - JG66805710</v>
       </c>
@@ -1914,30 +1918,30 @@
         <f aca="false">LEFT(F16,1)</f>
         <v>A</v>
       </c>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <f aca="false">IF(Sheet1!A17="","",Sheet1!A17)</f>
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="str">
+      <c r="B17" s="6" t="str">
         <f aca="false">IF(Sheet1!B17="","",Sheet1!B17)</f>
         <v>CH36848865</v>
       </c>
-      <c r="C17" s="5" t="str">
+      <c r="C17" s="6" t="str">
         <f aca="false">IF(Sheet1!C17="","",Sheet1!C17)</f>
         <v>Abramo</v>
       </c>
-      <c r="D17" s="5" t="str">
+      <c r="D17" s="6" t="str">
         <f aca="false">IF(Sheet1!D17="","",Sheet1!D17)</f>
         <v>Cafarella</v>
       </c>
-      <c r="E17" s="5" t="str">
+      <c r="E17" s="6" t="str">
         <f aca="false">IF(Sheet1!E17="","",Sheet1!E17)</f>
         <v>Abramo, Cafarella</v>
       </c>
-      <c r="F17" s="5" t="str">
+      <c r="F17" s="6" t="str">
         <f aca="false">IF(Sheet1!F17="","",Sheet1!F17)</f>
         <v>Abramo, Cafarella - CH36848865</v>
       </c>
@@ -1945,30 +1949,30 @@
         <f aca="false">LEFT(F17,1)</f>
         <v>A</v>
       </c>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <f aca="false">IF(Sheet1!A18="","",Sheet1!A18)</f>
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="str">
+      <c r="B18" s="6" t="str">
         <f aca="false">IF(Sheet1!B18="","",Sheet1!B18)</f>
         <v>CL41033165</v>
       </c>
-      <c r="C18" s="5" t="str">
+      <c r="C18" s="6" t="str">
         <f aca="false">IF(Sheet1!C18="","",Sheet1!C18)</f>
         <v>Absalon</v>
       </c>
-      <c r="D18" s="5" t="str">
+      <c r="D18" s="6" t="str">
         <f aca="false">IF(Sheet1!D18="","",Sheet1!D18)</f>
         <v>Cafarelli</v>
       </c>
-      <c r="E18" s="5" t="str">
+      <c r="E18" s="6" t="str">
         <f aca="false">IF(Sheet1!E18="","",Sheet1!E18)</f>
         <v>Absalon, Cafarelli</v>
       </c>
-      <c r="F18" s="5" t="str">
+      <c r="F18" s="6" t="str">
         <f aca="false">IF(Sheet1!F18="","",Sheet1!F18)</f>
         <v>Absalon, Cafarelli - CL41033165</v>
       </c>
@@ -1976,30 +1980,30 @@
         <f aca="false">LEFT(F18,1)</f>
         <v>A</v>
       </c>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <f aca="false">IF(Sheet1!A19="","",Sheet1!A19)</f>
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="str">
+      <c r="B19" s="6" t="str">
         <f aca="false">IF(Sheet1!B19="","",Sheet1!B19)</f>
         <v>LL21590248</v>
       </c>
-      <c r="C19" s="5" t="str">
+      <c r="C19" s="6" t="str">
         <f aca="false">IF(Sheet1!C19="","",Sheet1!C19)</f>
         <v>Abselon</v>
       </c>
-      <c r="D19" s="5" t="str">
+      <c r="D19" s="6" t="str">
         <f aca="false">IF(Sheet1!D19="","",Sheet1!D19)</f>
         <v>Cafaro</v>
       </c>
-      <c r="E19" s="5" t="str">
+      <c r="E19" s="6" t="str">
         <f aca="false">IF(Sheet1!E19="","",Sheet1!E19)</f>
         <v>Abselon, Cafaro</v>
       </c>
-      <c r="F19" s="5" t="str">
+      <c r="F19" s="6" t="str">
         <f aca="false">IF(Sheet1!F19="","",Sheet1!F19)</f>
         <v>Abselon, Cafaro - LL21590248</v>
       </c>
@@ -2007,30 +2011,30 @@
         <f aca="false">LEFT(F19,1)</f>
         <v>A</v>
       </c>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <f aca="false">IF(Sheet1!A20="","",Sheet1!A20)</f>
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="str">
+      <c r="B20" s="6" t="str">
         <f aca="false">IF(Sheet1!B20="","",Sheet1!B20)</f>
         <v>RK32756907</v>
       </c>
-      <c r="C20" s="5" t="str">
+      <c r="C20" s="6" t="str">
         <f aca="false">IF(Sheet1!C20="","",Sheet1!C20)</f>
         <v>Absolom</v>
       </c>
-      <c r="D20" s="5" t="str">
+      <c r="D20" s="6" t="str">
         <f aca="false">IF(Sheet1!D20="","",Sheet1!D20)</f>
         <v>Cafasso</v>
       </c>
-      <c r="E20" s="5" t="str">
+      <c r="E20" s="6" t="str">
         <f aca="false">IF(Sheet1!E20="","",Sheet1!E20)</f>
         <v>Absolom, Cafasso</v>
       </c>
-      <c r="F20" s="5" t="str">
+      <c r="F20" s="6" t="str">
         <f aca="false">IF(Sheet1!F20="","",Sheet1!F20)</f>
         <v>Absolom, Cafasso - RK32756907</v>
       </c>
@@ -2038,30 +2042,30 @@
         <f aca="false">LEFT(F20,1)</f>
         <v>A</v>
       </c>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <f aca="false">IF(Sheet1!A21="","",Sheet1!A21)</f>
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="str">
+      <c r="B21" s="6" t="str">
         <f aca="false">IF(Sheet1!B21="","",Sheet1!B21)</f>
         <v>EM26000697</v>
       </c>
-      <c r="C21" s="5" t="str">
+      <c r="C21" s="6" t="str">
         <f aca="false">IF(Sheet1!C21="","",Sheet1!C21)</f>
         <v>Absolum</v>
       </c>
-      <c r="D21" s="5" t="str">
+      <c r="D21" s="6" t="str">
         <f aca="false">IF(Sheet1!D21="","",Sheet1!D21)</f>
         <v>Caggiano</v>
       </c>
-      <c r="E21" s="5" t="str">
+      <c r="E21" s="6" t="str">
         <f aca="false">IF(Sheet1!E21="","",Sheet1!E21)</f>
         <v>Absolum, Caggiano</v>
       </c>
-      <c r="F21" s="5" t="str">
+      <c r="F21" s="6" t="str">
         <f aca="false">IF(Sheet1!F21="","",Sheet1!F21)</f>
         <v>Absolum, Caggiano - EM26000697</v>
       </c>
@@ -2069,62 +2073,62 @@
         <f aca="false">LEFT(F21,1)</f>
         <v>A</v>
       </c>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <f aca="false">IF(Sheet1!A22="","",Sheet1!A22)</f>
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="str">
+      <c r="B22" s="6" t="str">
         <f aca="false">IF(Sheet1!B22="","",Sheet1!B22)</f>
         <v>MM12168514</v>
       </c>
-      <c r="C22" s="5" t="str">
+      <c r="C22" s="6" t="str">
         <f aca="false">IF(Sheet1!C22="","",Sheet1!C22)</f>
         <v>Tbnor</v>
       </c>
-      <c r="D22" s="5" t="str">
+      <c r="D22" s="6" t="str">
         <f aca="false">IF(Sheet1!D22="","",Sheet1!D22)</f>
         <v>Cadigan</v>
       </c>
-      <c r="E22" s="5" t="str">
+      <c r="E22" s="6" t="str">
         <f aca="false">IF(Sheet1!E22="","",Sheet1!E22)</f>
         <v>Tbnor, Cadigan</v>
       </c>
-      <c r="F22" s="5" t="str">
+      <c r="F22" s="6" t="str">
         <f aca="false">IF(Sheet1!F22="","",Sheet1!F22)</f>
         <v>Tbnor, Cadigan - MM12168514</v>
       </c>
-      <c r="G22" s="8" t="str">
+      <c r="G22" s="9" t="str">
         <f aca="false">LEFT(F22,1)</f>
         <v>T</v>
       </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="10"/>
+      <c r="I22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <f aca="false">IF(Sheet1!A23="","",Sheet1!A23)</f>
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="str">
+      <c r="B23" s="6" t="str">
         <f aca="false">IF(Sheet1!B23="","",Sheet1!B23)</f>
         <v>HO10339330</v>
       </c>
-      <c r="C23" s="5" t="str">
+      <c r="C23" s="6" t="str">
         <f aca="false">IF(Sheet1!C23="","",Sheet1!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="5" t="str">
+      <c r="D23" s="6" t="str">
         <f aca="false">IF(Sheet1!D23="","",Sheet1!D23)</f>
         <v/>
       </c>
-      <c r="E23" s="5" t="str">
+      <c r="E23" s="6" t="str">
         <f aca="false">IF(Sheet1!E23="","",Sheet1!E23)</f>
         <v/>
       </c>
-      <c r="F23" s="5" t="str">
+      <c r="F23" s="6" t="str">
         <f aca="false">IF(Sheet1!F23="","",Sheet1!F23)</f>
         <v/>
       </c>
@@ -2132,30 +2136,30 @@
         <f aca="false">LEFT(F23,1)</f>
         <v/>
       </c>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <f aca="false">IF(Sheet1!A24="","",Sheet1!A24)</f>
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="str">
+      <c r="B24" s="6" t="str">
         <f aca="false">IF(Sheet1!B24="","",Sheet1!B24)</f>
         <v>RS31728184</v>
       </c>
-      <c r="C24" s="5" t="str">
+      <c r="C24" s="6" t="str">
         <f aca="false">IF(Sheet1!C24="","",Sheet1!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="5" t="str">
+      <c r="D24" s="6" t="str">
         <f aca="false">IF(Sheet1!D24="","",Sheet1!D24)</f>
         <v/>
       </c>
-      <c r="E24" s="5" t="str">
+      <c r="E24" s="6" t="str">
         <f aca="false">IF(Sheet1!E24="","",Sheet1!E24)</f>
         <v/>
       </c>
-      <c r="F24" s="5" t="str">
+      <c r="F24" s="6" t="str">
         <f aca="false">IF(Sheet1!F24="","",Sheet1!F24)</f>
         <v/>
       </c>
@@ -2163,30 +2167,30 @@
         <f aca="false">LEFT(F24,1)</f>
         <v/>
       </c>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <f aca="false">IF(Sheet1!A25="","",Sheet1!A25)</f>
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="str">
+      <c r="B25" s="6" t="str">
         <f aca="false">IF(Sheet1!B25="","",Sheet1!B25)</f>
         <v>SS43010028</v>
       </c>
-      <c r="C25" s="5" t="str">
+      <c r="C25" s="6" t="str">
         <f aca="false">IF(Sheet1!C25="","",Sheet1!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="5" t="str">
+      <c r="D25" s="6" t="str">
         <f aca="false">IF(Sheet1!D25="","",Sheet1!D25)</f>
         <v/>
       </c>
-      <c r="E25" s="5" t="str">
+      <c r="E25" s="6" t="str">
         <f aca="false">IF(Sheet1!E25="","",Sheet1!E25)</f>
         <v/>
       </c>
-      <c r="F25" s="5" t="str">
+      <c r="F25" s="6" t="str">
         <f aca="false">IF(Sheet1!F25="","",Sheet1!F25)</f>
         <v/>
       </c>
@@ -2194,30 +2198,30 @@
         <f aca="false">LEFT(F25,1)</f>
         <v/>
       </c>
-      <c r="I25" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <f aca="false">IF(Sheet1!A26="","",Sheet1!A26)</f>
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="str">
+      <c r="B26" s="6" t="str">
         <f aca="false">IF(Sheet1!B26="","",Sheet1!B26)</f>
         <v>TT33991592</v>
       </c>
-      <c r="C26" s="5" t="str">
+      <c r="C26" s="6" t="str">
         <f aca="false">IF(Sheet1!C26="","",Sheet1!C26)</f>
         <v/>
       </c>
-      <c r="D26" s="5" t="str">
+      <c r="D26" s="6" t="str">
         <f aca="false">IF(Sheet1!D26="","",Sheet1!D26)</f>
         <v/>
       </c>
-      <c r="E26" s="5" t="str">
+      <c r="E26" s="6" t="str">
         <f aca="false">IF(Sheet1!E26="","",Sheet1!E26)</f>
         <v/>
       </c>
-      <c r="F26" s="5" t="str">
+      <c r="F26" s="6" t="str">
         <f aca="false">IF(Sheet1!F26="","",Sheet1!F26)</f>
         <v/>
       </c>
@@ -2225,30 +2229,30 @@
         <f aca="false">LEFT(F26,1)</f>
         <v/>
       </c>
-      <c r="I26" s="12"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <f aca="false">IF(Sheet1!A27="","",Sheet1!A27)</f>
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="str">
+      <c r="B27" s="6" t="str">
         <f aca="false">IF(Sheet1!B27="","",Sheet1!B27)</f>
         <v>CV22833553</v>
       </c>
-      <c r="C27" s="5" t="str">
+      <c r="C27" s="6" t="str">
         <f aca="false">IF(Sheet1!C27="","",Sheet1!C27)</f>
         <v/>
       </c>
-      <c r="D27" s="5" t="str">
+      <c r="D27" s="6" t="str">
         <f aca="false">IF(Sheet1!D27="","",Sheet1!D27)</f>
         <v/>
       </c>
-      <c r="E27" s="5" t="str">
+      <c r="E27" s="6" t="str">
         <f aca="false">IF(Sheet1!E27="","",Sheet1!E27)</f>
         <v/>
       </c>
-      <c r="F27" s="5" t="str">
+      <c r="F27" s="6" t="str">
         <f aca="false">IF(Sheet1!F27="","",Sheet1!F27)</f>
         <v/>
       </c>
@@ -2256,30 +2260,30 @@
         <f aca="false">LEFT(F27,1)</f>
         <v/>
       </c>
-      <c r="I27" s="12"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="13"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="str">
         <f aca="false">IF(Sheet1!A28="","",Sheet1!A28)</f>
         <v/>
       </c>
-      <c r="B28" s="5" t="str">
+      <c r="B28" s="6" t="str">
         <f aca="false">IF(Sheet1!B28="","",Sheet1!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="5" t="str">
+      <c r="C28" s="6" t="str">
         <f aca="false">IF(Sheet1!C28="","",Sheet1!C28)</f>
         <v/>
       </c>
-      <c r="D28" s="5" t="str">
+      <c r="D28" s="6" t="str">
         <f aca="false">IF(Sheet1!D28="","",Sheet1!D28)</f>
         <v/>
       </c>
-      <c r="E28" s="5" t="str">
+      <c r="E28" s="6" t="str">
         <f aca="false">IF(Sheet1!E28="","",Sheet1!E28)</f>
         <v/>
       </c>
-      <c r="F28" s="5" t="str">
+      <c r="F28" s="6" t="str">
         <f aca="false">IF(Sheet1!F28="","",Sheet1!F28)</f>
         <v/>
       </c>
@@ -2287,30 +2291,30 @@
         <f aca="false">LEFT(F28,1)</f>
         <v/>
       </c>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="str">
         <f aca="false">IF(Sheet1!A29="","",Sheet1!A29)</f>
         <v/>
       </c>
-      <c r="B29" s="5" t="str">
+      <c r="B29" s="6" t="str">
         <f aca="false">IF(Sheet1!B29="","",Sheet1!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="5" t="str">
+      <c r="C29" s="6" t="str">
         <f aca="false">IF(Sheet1!C29="","",Sheet1!C29)</f>
         <v/>
       </c>
-      <c r="D29" s="5" t="str">
+      <c r="D29" s="6" t="str">
         <f aca="false">IF(Sheet1!D29="","",Sheet1!D29)</f>
         <v/>
       </c>
-      <c r="E29" s="5" t="str">
+      <c r="E29" s="6" t="str">
         <f aca="false">IF(Sheet1!E29="","",Sheet1!E29)</f>
         <v/>
       </c>
-      <c r="F29" s="5" t="str">
+      <c r="F29" s="6" t="str">
         <f aca="false">IF(Sheet1!F29="","",Sheet1!F29)</f>
         <v/>
       </c>
@@ -2318,30 +2322,30 @@
         <f aca="false">LEFT(F29,1)</f>
         <v/>
       </c>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="13"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="str">
         <f aca="false">IF(Sheet1!A30="","",Sheet1!A30)</f>
         <v/>
       </c>
-      <c r="B30" s="5" t="str">
+      <c r="B30" s="6" t="str">
         <f aca="false">IF(Sheet1!B30="","",Sheet1!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="5" t="str">
+      <c r="C30" s="6" t="str">
         <f aca="false">IF(Sheet1!C30="","",Sheet1!C30)</f>
         <v/>
       </c>
-      <c r="D30" s="5" t="str">
+      <c r="D30" s="6" t="str">
         <f aca="false">IF(Sheet1!D30="","",Sheet1!D30)</f>
         <v/>
       </c>
-      <c r="E30" s="5" t="str">
+      <c r="E30" s="6" t="str">
         <f aca="false">IF(Sheet1!E30="","",Sheet1!E30)</f>
         <v/>
       </c>
-      <c r="F30" s="5" t="str">
+      <c r="F30" s="6" t="str">
         <f aca="false">IF(Sheet1!F30="","",Sheet1!F30)</f>
         <v/>
       </c>
@@ -2349,30 +2353,30 @@
         <f aca="false">LEFT(F30,1)</f>
         <v/>
       </c>
-      <c r="I30" s="12"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="str">
         <f aca="false">IF(Sheet1!A31="","",Sheet1!A31)</f>
         <v/>
       </c>
-      <c r="B31" s="5" t="str">
+      <c r="B31" s="6" t="str">
         <f aca="false">IF(Sheet1!B31="","",Sheet1!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="5" t="str">
+      <c r="C31" s="6" t="str">
         <f aca="false">IF(Sheet1!C31="","",Sheet1!C31)</f>
         <v/>
       </c>
-      <c r="D31" s="5" t="str">
+      <c r="D31" s="6" t="str">
         <f aca="false">IF(Sheet1!D31="","",Sheet1!D31)</f>
         <v/>
       </c>
-      <c r="E31" s="5" t="str">
+      <c r="E31" s="6" t="str">
         <f aca="false">IF(Sheet1!E31="","",Sheet1!E31)</f>
         <v/>
       </c>
-      <c r="F31" s="5" t="str">
+      <c r="F31" s="6" t="str">
         <f aca="false">IF(Sheet1!F31="","",Sheet1!F31)</f>
         <v/>
       </c>
@@ -2380,30 +2384,30 @@
         <f aca="false">LEFT(F31,1)</f>
         <v/>
       </c>
-      <c r="I31" s="12"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="str">
         <f aca="false">IF(Sheet1!A32="","",Sheet1!A32)</f>
         <v/>
       </c>
-      <c r="B32" s="5" t="str">
+      <c r="B32" s="6" t="str">
         <f aca="false">IF(Sheet1!B32="","",Sheet1!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="5" t="str">
+      <c r="C32" s="6" t="str">
         <f aca="false">IF(Sheet1!C32="","",Sheet1!C32)</f>
         <v/>
       </c>
-      <c r="D32" s="5" t="str">
+      <c r="D32" s="6" t="str">
         <f aca="false">IF(Sheet1!D32="","",Sheet1!D32)</f>
         <v/>
       </c>
-      <c r="E32" s="5" t="str">
+      <c r="E32" s="6" t="str">
         <f aca="false">IF(Sheet1!E32="","",Sheet1!E32)</f>
         <v/>
       </c>
-      <c r="F32" s="5" t="str">
+      <c r="F32" s="6" t="str">
         <f aca="false">IF(Sheet1!F32="","",Sheet1!F32)</f>
         <v/>
       </c>
@@ -2411,30 +2415,30 @@
         <f aca="false">LEFT(F32,1)</f>
         <v/>
       </c>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="str">
         <f aca="false">IF(Sheet1!A33="","",Sheet1!A33)</f>
         <v/>
       </c>
-      <c r="B33" s="5" t="str">
+      <c r="B33" s="6" t="str">
         <f aca="false">IF(Sheet1!B33="","",Sheet1!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="5" t="str">
+      <c r="C33" s="6" t="str">
         <f aca="false">IF(Sheet1!C33="","",Sheet1!C33)</f>
         <v/>
       </c>
-      <c r="D33" s="5" t="str">
+      <c r="D33" s="6" t="str">
         <f aca="false">IF(Sheet1!D33="","",Sheet1!D33)</f>
         <v/>
       </c>
-      <c r="E33" s="5" t="str">
+      <c r="E33" s="6" t="str">
         <f aca="false">IF(Sheet1!E33="","",Sheet1!E33)</f>
         <v/>
       </c>
-      <c r="F33" s="5" t="str">
+      <c r="F33" s="6" t="str">
         <f aca="false">IF(Sheet1!F33="","",Sheet1!F33)</f>
         <v/>
       </c>
@@ -2442,30 +2446,30 @@
         <f aca="false">LEFT(F33,1)</f>
         <v/>
       </c>
-      <c r="I33" s="12"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="str">
         <f aca="false">IF(Sheet1!A34="","",Sheet1!A34)</f>
         <v/>
       </c>
-      <c r="B34" s="5" t="str">
+      <c r="B34" s="6" t="str">
         <f aca="false">IF(Sheet1!B34="","",Sheet1!B34)</f>
         <v/>
       </c>
-      <c r="C34" s="5" t="str">
+      <c r="C34" s="6" t="str">
         <f aca="false">IF(Sheet1!C34="","",Sheet1!C34)</f>
         <v/>
       </c>
-      <c r="D34" s="5" t="str">
+      <c r="D34" s="6" t="str">
         <f aca="false">IF(Sheet1!D34="","",Sheet1!D34)</f>
         <v/>
       </c>
-      <c r="E34" s="5" t="str">
+      <c r="E34" s="6" t="str">
         <f aca="false">IF(Sheet1!E34="","",Sheet1!E34)</f>
         <v/>
       </c>
-      <c r="F34" s="5" t="str">
+      <c r="F34" s="6" t="str">
         <f aca="false">IF(Sheet1!F34="","",Sheet1!F34)</f>
         <v/>
       </c>
@@ -2473,30 +2477,30 @@
         <f aca="false">LEFT(F34,1)</f>
         <v/>
       </c>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="str">
         <f aca="false">IF(Sheet1!A35="","",Sheet1!A35)</f>
         <v/>
       </c>
-      <c r="B35" s="5" t="str">
+      <c r="B35" s="6" t="str">
         <f aca="false">IF(Sheet1!B35="","",Sheet1!B35)</f>
         <v/>
       </c>
-      <c r="C35" s="5" t="str">
+      <c r="C35" s="6" t="str">
         <f aca="false">IF(Sheet1!C35="","",Sheet1!C35)</f>
         <v/>
       </c>
-      <c r="D35" s="5" t="str">
+      <c r="D35" s="6" t="str">
         <f aca="false">IF(Sheet1!D35="","",Sheet1!D35)</f>
         <v/>
       </c>
-      <c r="E35" s="5" t="str">
+      <c r="E35" s="6" t="str">
         <f aca="false">IF(Sheet1!E35="","",Sheet1!E35)</f>
         <v/>
       </c>
-      <c r="F35" s="5" t="str">
+      <c r="F35" s="6" t="str">
         <f aca="false">IF(Sheet1!F35="","",Sheet1!F35)</f>
         <v/>
       </c>
@@ -2504,30 +2508,30 @@
         <f aca="false">LEFT(F35,1)</f>
         <v/>
       </c>
-      <c r="I35" s="12"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="str">
         <f aca="false">IF(Sheet1!A36="","",Sheet1!A36)</f>
         <v/>
       </c>
-      <c r="B36" s="5" t="str">
+      <c r="B36" s="6" t="str">
         <f aca="false">IF(Sheet1!B36="","",Sheet1!B36)</f>
         <v/>
       </c>
-      <c r="C36" s="5" t="str">
+      <c r="C36" s="6" t="str">
         <f aca="false">IF(Sheet1!C36="","",Sheet1!C36)</f>
         <v/>
       </c>
-      <c r="D36" s="5" t="str">
+      <c r="D36" s="6" t="str">
         <f aca="false">IF(Sheet1!D36="","",Sheet1!D36)</f>
         <v/>
       </c>
-      <c r="E36" s="5" t="str">
+      <c r="E36" s="6" t="str">
         <f aca="false">IF(Sheet1!E36="","",Sheet1!E36)</f>
         <v/>
       </c>
-      <c r="F36" s="5" t="str">
+      <c r="F36" s="6" t="str">
         <f aca="false">IF(Sheet1!F36="","",Sheet1!F36)</f>
         <v/>
       </c>
@@ -2535,30 +2539,30 @@
         <f aca="false">LEFT(F36,1)</f>
         <v/>
       </c>
-      <c r="I36" s="12"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="str">
         <f aca="false">IF(Sheet1!A37="","",Sheet1!A37)</f>
         <v/>
       </c>
-      <c r="B37" s="5" t="str">
+      <c r="B37" s="6" t="str">
         <f aca="false">IF(Sheet1!B37="","",Sheet1!B37)</f>
         <v/>
       </c>
-      <c r="C37" s="5" t="str">
+      <c r="C37" s="6" t="str">
         <f aca="false">IF(Sheet1!C37="","",Sheet1!C37)</f>
         <v/>
       </c>
-      <c r="D37" s="5" t="str">
+      <c r="D37" s="6" t="str">
         <f aca="false">IF(Sheet1!D37="","",Sheet1!D37)</f>
         <v/>
       </c>
-      <c r="E37" s="5" t="str">
+      <c r="E37" s="6" t="str">
         <f aca="false">IF(Sheet1!E37="","",Sheet1!E37)</f>
         <v/>
       </c>
-      <c r="F37" s="5" t="str">
+      <c r="F37" s="6" t="str">
         <f aca="false">IF(Sheet1!F37="","",Sheet1!F37)</f>
         <v/>
       </c>
@@ -2566,30 +2570,30 @@
         <f aca="false">LEFT(F37,1)</f>
         <v/>
       </c>
-      <c r="I37" s="12"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="str">
         <f aca="false">IF(Sheet1!A38="","",Sheet1!A38)</f>
         <v/>
       </c>
-      <c r="B38" s="5" t="str">
+      <c r="B38" s="6" t="str">
         <f aca="false">IF(Sheet1!B38="","",Sheet1!B38)</f>
         <v/>
       </c>
-      <c r="C38" s="5" t="str">
+      <c r="C38" s="6" t="str">
         <f aca="false">IF(Sheet1!C38="","",Sheet1!C38)</f>
         <v/>
       </c>
-      <c r="D38" s="5" t="str">
+      <c r="D38" s="6" t="str">
         <f aca="false">IF(Sheet1!D38="","",Sheet1!D38)</f>
         <v/>
       </c>
-      <c r="E38" s="5" t="str">
+      <c r="E38" s="6" t="str">
         <f aca="false">IF(Sheet1!E38="","",Sheet1!E38)</f>
         <v/>
       </c>
-      <c r="F38" s="5" t="str">
+      <c r="F38" s="6" t="str">
         <f aca="false">IF(Sheet1!F38="","",Sheet1!F38)</f>
         <v/>
       </c>
@@ -2597,30 +2601,30 @@
         <f aca="false">LEFT(F38,1)</f>
         <v/>
       </c>
-      <c r="I38" s="12"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="str">
         <f aca="false">IF(Sheet1!A39="","",Sheet1!A39)</f>
         <v/>
       </c>
-      <c r="B39" s="5" t="str">
+      <c r="B39" s="6" t="str">
         <f aca="false">IF(Sheet1!B39="","",Sheet1!B39)</f>
         <v/>
       </c>
-      <c r="C39" s="5" t="str">
+      <c r="C39" s="6" t="str">
         <f aca="false">IF(Sheet1!C39="","",Sheet1!C39)</f>
         <v/>
       </c>
-      <c r="D39" s="5" t="str">
+      <c r="D39" s="6" t="str">
         <f aca="false">IF(Sheet1!D39="","",Sheet1!D39)</f>
         <v/>
       </c>
-      <c r="E39" s="5" t="str">
+      <c r="E39" s="6" t="str">
         <f aca="false">IF(Sheet1!E39="","",Sheet1!E39)</f>
         <v/>
       </c>
-      <c r="F39" s="5" t="str">
+      <c r="F39" s="6" t="str">
         <f aca="false">IF(Sheet1!F39="","",Sheet1!F39)</f>
         <v/>
       </c>
@@ -2628,30 +2632,30 @@
         <f aca="false">LEFT(F39,1)</f>
         <v/>
       </c>
-      <c r="I39" s="12"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="str">
         <f aca="false">IF(Sheet1!A40="","",Sheet1!A40)</f>
         <v/>
       </c>
-      <c r="B40" s="5" t="str">
+      <c r="B40" s="6" t="str">
         <f aca="false">IF(Sheet1!B40="","",Sheet1!B40)</f>
         <v/>
       </c>
-      <c r="C40" s="5" t="str">
+      <c r="C40" s="6" t="str">
         <f aca="false">IF(Sheet1!C40="","",Sheet1!C40)</f>
         <v/>
       </c>
-      <c r="D40" s="5" t="str">
+      <c r="D40" s="6" t="str">
         <f aca="false">IF(Sheet1!D40="","",Sheet1!D40)</f>
         <v/>
       </c>
-      <c r="E40" s="5" t="str">
+      <c r="E40" s="6" t="str">
         <f aca="false">IF(Sheet1!E40="","",Sheet1!E40)</f>
         <v/>
       </c>
-      <c r="F40" s="5" t="str">
+      <c r="F40" s="6" t="str">
         <f aca="false">IF(Sheet1!F40="","",Sheet1!F40)</f>
         <v/>
       </c>
@@ -2659,30 +2663,30 @@
         <f aca="false">LEFT(F40,1)</f>
         <v/>
       </c>
-      <c r="I40" s="12"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="str">
         <f aca="false">IF(Sheet1!A41="","",Sheet1!A41)</f>
         <v/>
       </c>
-      <c r="B41" s="5" t="str">
+      <c r="B41" s="6" t="str">
         <f aca="false">IF(Sheet1!B41="","",Sheet1!B41)</f>
         <v/>
       </c>
-      <c r="C41" s="5" t="str">
+      <c r="C41" s="6" t="str">
         <f aca="false">IF(Sheet1!C41="","",Sheet1!C41)</f>
         <v/>
       </c>
-      <c r="D41" s="5" t="str">
+      <c r="D41" s="6" t="str">
         <f aca="false">IF(Sheet1!D41="","",Sheet1!D41)</f>
         <v/>
       </c>
-      <c r="E41" s="5" t="str">
+      <c r="E41" s="6" t="str">
         <f aca="false">IF(Sheet1!E41="","",Sheet1!E41)</f>
         <v/>
       </c>
-      <c r="F41" s="5" t="str">
+      <c r="F41" s="6" t="str">
         <f aca="false">IF(Sheet1!F41="","",Sheet1!F41)</f>
         <v/>
       </c>
@@ -2690,30 +2694,30 @@
         <f aca="false">LEFT(F41,1)</f>
         <v/>
       </c>
-      <c r="I41" s="12"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="str">
         <f aca="false">IF(Sheet1!A42="","",Sheet1!A42)</f>
         <v/>
       </c>
-      <c r="B42" s="5" t="str">
+      <c r="B42" s="6" t="str">
         <f aca="false">IF(Sheet1!B42="","",Sheet1!B42)</f>
         <v/>
       </c>
-      <c r="C42" s="5" t="str">
+      <c r="C42" s="6" t="str">
         <f aca="false">IF(Sheet1!C42="","",Sheet1!C42)</f>
         <v/>
       </c>
-      <c r="D42" s="5" t="str">
+      <c r="D42" s="6" t="str">
         <f aca="false">IF(Sheet1!D42="","",Sheet1!D42)</f>
         <v/>
       </c>
-      <c r="E42" s="5" t="str">
+      <c r="E42" s="6" t="str">
         <f aca="false">IF(Sheet1!E42="","",Sheet1!E42)</f>
         <v/>
       </c>
-      <c r="F42" s="5" t="str">
+      <c r="F42" s="6" t="str">
         <f aca="false">IF(Sheet1!F42="","",Sheet1!F42)</f>
         <v/>
       </c>
@@ -2721,30 +2725,30 @@
         <f aca="false">LEFT(F42,1)</f>
         <v/>
       </c>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="str">
         <f aca="false">IF(Sheet1!A43="","",Sheet1!A43)</f>
         <v/>
       </c>
-      <c r="B43" s="5" t="str">
+      <c r="B43" s="6" t="str">
         <f aca="false">IF(Sheet1!B43="","",Sheet1!B43)</f>
         <v/>
       </c>
-      <c r="C43" s="5" t="str">
+      <c r="C43" s="6" t="str">
         <f aca="false">IF(Sheet1!C43="","",Sheet1!C43)</f>
         <v/>
       </c>
-      <c r="D43" s="5" t="str">
+      <c r="D43" s="6" t="str">
         <f aca="false">IF(Sheet1!D43="","",Sheet1!D43)</f>
         <v/>
       </c>
-      <c r="E43" s="5" t="str">
+      <c r="E43" s="6" t="str">
         <f aca="false">IF(Sheet1!E43="","",Sheet1!E43)</f>
         <v/>
       </c>
-      <c r="F43" s="5" t="str">
+      <c r="F43" s="6" t="str">
         <f aca="false">IF(Sheet1!F43="","",Sheet1!F43)</f>
         <v/>
       </c>
@@ -2752,30 +2756,30 @@
         <f aca="false">LEFT(F43,1)</f>
         <v/>
       </c>
-      <c r="I43" s="12"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="str">
         <f aca="false">IF(Sheet1!A44="","",Sheet1!A44)</f>
         <v/>
       </c>
-      <c r="B44" s="5" t="str">
+      <c r="B44" s="6" t="str">
         <f aca="false">IF(Sheet1!B44="","",Sheet1!B44)</f>
         <v/>
       </c>
-      <c r="C44" s="5" t="str">
+      <c r="C44" s="6" t="str">
         <f aca="false">IF(Sheet1!C44="","",Sheet1!C44)</f>
         <v/>
       </c>
-      <c r="D44" s="5" t="str">
+      <c r="D44" s="6" t="str">
         <f aca="false">IF(Sheet1!D44="","",Sheet1!D44)</f>
         <v/>
       </c>
-      <c r="E44" s="5" t="str">
+      <c r="E44" s="6" t="str">
         <f aca="false">IF(Sheet1!E44="","",Sheet1!E44)</f>
         <v/>
       </c>
-      <c r="F44" s="5" t="str">
+      <c r="F44" s="6" t="str">
         <f aca="false">IF(Sheet1!F44="","",Sheet1!F44)</f>
         <v/>
       </c>
@@ -2783,30 +2787,30 @@
         <f aca="false">LEFT(F44,1)</f>
         <v/>
       </c>
-      <c r="I44" s="12"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="13"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="str">
         <f aca="false">IF(Sheet1!A45="","",Sheet1!A45)</f>
         <v/>
       </c>
-      <c r="B45" s="5" t="str">
+      <c r="B45" s="6" t="str">
         <f aca="false">IF(Sheet1!B45="","",Sheet1!B45)</f>
         <v/>
       </c>
-      <c r="C45" s="5" t="str">
+      <c r="C45" s="6" t="str">
         <f aca="false">IF(Sheet1!C45="","",Sheet1!C45)</f>
         <v/>
       </c>
-      <c r="D45" s="5" t="str">
+      <c r="D45" s="6" t="str">
         <f aca="false">IF(Sheet1!D45="","",Sheet1!D45)</f>
         <v/>
       </c>
-      <c r="E45" s="5" t="str">
+      <c r="E45" s="6" t="str">
         <f aca="false">IF(Sheet1!E45="","",Sheet1!E45)</f>
         <v/>
       </c>
-      <c r="F45" s="5" t="str">
+      <c r="F45" s="6" t="str">
         <f aca="false">IF(Sheet1!F45="","",Sheet1!F45)</f>
         <v/>
       </c>
@@ -2814,30 +2818,30 @@
         <f aca="false">LEFT(F45,1)</f>
         <v/>
       </c>
-      <c r="I45" s="12"/>
-    </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I45" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="str">
         <f aca="false">IF(Sheet1!A46="","",Sheet1!A46)</f>
         <v/>
       </c>
-      <c r="B46" s="5" t="str">
+      <c r="B46" s="6" t="str">
         <f aca="false">IF(Sheet1!B46="","",Sheet1!B46)</f>
         <v/>
       </c>
-      <c r="C46" s="5" t="str">
+      <c r="C46" s="6" t="str">
         <f aca="false">IF(Sheet1!C46="","",Sheet1!C46)</f>
         <v/>
       </c>
-      <c r="D46" s="5" t="str">
+      <c r="D46" s="6" t="str">
         <f aca="false">IF(Sheet1!D46="","",Sheet1!D46)</f>
         <v/>
       </c>
-      <c r="E46" s="5" t="str">
+      <c r="E46" s="6" t="str">
         <f aca="false">IF(Sheet1!E46="","",Sheet1!E46)</f>
         <v/>
       </c>
-      <c r="F46" s="5" t="str">
+      <c r="F46" s="6" t="str">
         <f aca="false">IF(Sheet1!F46="","",Sheet1!F46)</f>
         <v/>
       </c>
@@ -2845,30 +2849,30 @@
         <f aca="false">LEFT(F46,1)</f>
         <v/>
       </c>
-      <c r="I46" s="12"/>
-    </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I46" s="13"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="str">
         <f aca="false">IF(Sheet1!A47="","",Sheet1!A47)</f>
         <v/>
       </c>
-      <c r="B47" s="5" t="str">
+      <c r="B47" s="6" t="str">
         <f aca="false">IF(Sheet1!B47="","",Sheet1!B47)</f>
         <v/>
       </c>
-      <c r="C47" s="5" t="str">
+      <c r="C47" s="6" t="str">
         <f aca="false">IF(Sheet1!C47="","",Sheet1!C47)</f>
         <v/>
       </c>
-      <c r="D47" s="5" t="str">
+      <c r="D47" s="6" t="str">
         <f aca="false">IF(Sheet1!D47="","",Sheet1!D47)</f>
         <v/>
       </c>
-      <c r="E47" s="5" t="str">
+      <c r="E47" s="6" t="str">
         <f aca="false">IF(Sheet1!E47="","",Sheet1!E47)</f>
         <v/>
       </c>
-      <c r="F47" s="5" t="str">
+      <c r="F47" s="6" t="str">
         <f aca="false">IF(Sheet1!F47="","",Sheet1!F47)</f>
         <v/>
       </c>
@@ -2876,30 +2880,30 @@
         <f aca="false">LEFT(F47,1)</f>
         <v/>
       </c>
-      <c r="I47" s="12"/>
-    </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="13"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="str">
         <f aca="false">IF(Sheet1!A48="","",Sheet1!A48)</f>
         <v/>
       </c>
-      <c r="B48" s="5" t="str">
+      <c r="B48" s="6" t="str">
         <f aca="false">IF(Sheet1!B48="","",Sheet1!B48)</f>
         <v/>
       </c>
-      <c r="C48" s="5" t="str">
+      <c r="C48" s="6" t="str">
         <f aca="false">IF(Sheet1!C48="","",Sheet1!C48)</f>
         <v/>
       </c>
-      <c r="D48" s="5" t="str">
+      <c r="D48" s="6" t="str">
         <f aca="false">IF(Sheet1!D48="","",Sheet1!D48)</f>
         <v/>
       </c>
-      <c r="E48" s="5" t="str">
+      <c r="E48" s="6" t="str">
         <f aca="false">IF(Sheet1!E48="","",Sheet1!E48)</f>
         <v/>
       </c>
-      <c r="F48" s="5" t="str">
+      <c r="F48" s="6" t="str">
         <f aca="false">IF(Sheet1!F48="","",Sheet1!F48)</f>
         <v/>
       </c>
@@ -2907,30 +2911,30 @@
         <f aca="false">LEFT(F48,1)</f>
         <v/>
       </c>
-      <c r="I48" s="12"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="str">
         <f aca="false">IF(Sheet1!A49="","",Sheet1!A49)</f>
         <v/>
       </c>
-      <c r="B49" s="5" t="str">
+      <c r="B49" s="6" t="str">
         <f aca="false">IF(Sheet1!B49="","",Sheet1!B49)</f>
         <v/>
       </c>
-      <c r="C49" s="5" t="str">
+      <c r="C49" s="6" t="str">
         <f aca="false">IF(Sheet1!C49="","",Sheet1!C49)</f>
         <v/>
       </c>
-      <c r="D49" s="5" t="str">
+      <c r="D49" s="6" t="str">
         <f aca="false">IF(Sheet1!D49="","",Sheet1!D49)</f>
         <v/>
       </c>
-      <c r="E49" s="5" t="str">
+      <c r="E49" s="6" t="str">
         <f aca="false">IF(Sheet1!E49="","",Sheet1!E49)</f>
         <v/>
       </c>
-      <c r="F49" s="5" t="str">
+      <c r="F49" s="6" t="str">
         <f aca="false">IF(Sheet1!F49="","",Sheet1!F49)</f>
         <v/>
       </c>
@@ -2938,30 +2942,30 @@
         <f aca="false">LEFT(F49,1)</f>
         <v/>
       </c>
-      <c r="I49" s="12"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I49" s="13"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="str">
         <f aca="false">IF(Sheet1!A50="","",Sheet1!A50)</f>
         <v/>
       </c>
-      <c r="B50" s="5" t="str">
+      <c r="B50" s="6" t="str">
         <f aca="false">IF(Sheet1!B50="","",Sheet1!B50)</f>
         <v/>
       </c>
-      <c r="C50" s="5" t="str">
+      <c r="C50" s="6" t="str">
         <f aca="false">IF(Sheet1!C50="","",Sheet1!C50)</f>
         <v/>
       </c>
-      <c r="D50" s="5" t="str">
+      <c r="D50" s="6" t="str">
         <f aca="false">IF(Sheet1!D50="","",Sheet1!D50)</f>
         <v/>
       </c>
-      <c r="E50" s="5" t="str">
+      <c r="E50" s="6" t="str">
         <f aca="false">IF(Sheet1!E50="","",Sheet1!E50)</f>
         <v/>
       </c>
-      <c r="F50" s="5" t="str">
+      <c r="F50" s="6" t="str">
         <f aca="false">IF(Sheet1!F50="","",Sheet1!F50)</f>
         <v/>
       </c>
@@ -2969,30 +2973,30 @@
         <f aca="false">LEFT(F50,1)</f>
         <v/>
       </c>
-      <c r="I50" s="12"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="13"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="str">
         <f aca="false">IF(Sheet1!A51="","",Sheet1!A51)</f>
         <v/>
       </c>
-      <c r="B51" s="5" t="str">
+      <c r="B51" s="6" t="str">
         <f aca="false">IF(Sheet1!B51="","",Sheet1!B51)</f>
         <v/>
       </c>
-      <c r="C51" s="5" t="str">
+      <c r="C51" s="6" t="str">
         <f aca="false">IF(Sheet1!C51="","",Sheet1!C51)</f>
         <v/>
       </c>
-      <c r="D51" s="5" t="str">
+      <c r="D51" s="6" t="str">
         <f aca="false">IF(Sheet1!D51="","",Sheet1!D51)</f>
         <v/>
       </c>
-      <c r="E51" s="5" t="str">
+      <c r="E51" s="6" t="str">
         <f aca="false">IF(Sheet1!E51="","",Sheet1!E51)</f>
         <v/>
       </c>
-      <c r="F51" s="5" t="str">
+      <c r="F51" s="6" t="str">
         <f aca="false">IF(Sheet1!F51="","",Sheet1!F51)</f>
         <v/>
       </c>
@@ -3000,30 +3004,30 @@
         <f aca="false">LEFT(F51,1)</f>
         <v/>
       </c>
-      <c r="I51" s="12"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="13"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="str">
         <f aca="false">IF(Sheet1!A52="","",Sheet1!A52)</f>
         <v/>
       </c>
-      <c r="B52" s="5" t="str">
+      <c r="B52" s="6" t="str">
         <f aca="false">IF(Sheet1!B52="","",Sheet1!B52)</f>
         <v/>
       </c>
-      <c r="C52" s="5" t="str">
+      <c r="C52" s="6" t="str">
         <f aca="false">IF(Sheet1!C52="","",Sheet1!C52)</f>
         <v/>
       </c>
-      <c r="D52" s="5" t="str">
+      <c r="D52" s="6" t="str">
         <f aca="false">IF(Sheet1!D52="","",Sheet1!D52)</f>
         <v/>
       </c>
-      <c r="E52" s="5" t="str">
+      <c r="E52" s="6" t="str">
         <f aca="false">IF(Sheet1!E52="","",Sheet1!E52)</f>
         <v/>
       </c>
-      <c r="F52" s="5" t="str">
+      <c r="F52" s="6" t="str">
         <f aca="false">IF(Sheet1!F52="","",Sheet1!F52)</f>
         <v/>
       </c>
@@ -3031,30 +3035,30 @@
         <f aca="false">LEFT(F52,1)</f>
         <v/>
       </c>
-      <c r="I52" s="12"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="str">
         <f aca="false">IF(Sheet1!A53="","",Sheet1!A53)</f>
         <v/>
       </c>
-      <c r="B53" s="5" t="str">
+      <c r="B53" s="6" t="str">
         <f aca="false">IF(Sheet1!B53="","",Sheet1!B53)</f>
         <v/>
       </c>
-      <c r="C53" s="5" t="str">
+      <c r="C53" s="6" t="str">
         <f aca="false">IF(Sheet1!C53="","",Sheet1!C53)</f>
         <v/>
       </c>
-      <c r="D53" s="5" t="str">
+      <c r="D53" s="6" t="str">
         <f aca="false">IF(Sheet1!D53="","",Sheet1!D53)</f>
         <v/>
       </c>
-      <c r="E53" s="5" t="str">
+      <c r="E53" s="6" t="str">
         <f aca="false">IF(Sheet1!E53="","",Sheet1!E53)</f>
         <v/>
       </c>
-      <c r="F53" s="5" t="str">
+      <c r="F53" s="6" t="str">
         <f aca="false">IF(Sheet1!F53="","",Sheet1!F53)</f>
         <v/>
       </c>
@@ -3062,30 +3066,30 @@
         <f aca="false">LEFT(F53,1)</f>
         <v/>
       </c>
-      <c r="I53" s="12"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I53" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="str">
         <f aca="false">IF(Sheet1!A54="","",Sheet1!A54)</f>
         <v/>
       </c>
-      <c r="B54" s="5" t="str">
+      <c r="B54" s="6" t="str">
         <f aca="false">IF(Sheet1!B54="","",Sheet1!B54)</f>
         <v/>
       </c>
-      <c r="C54" s="5" t="str">
+      <c r="C54" s="6" t="str">
         <f aca="false">IF(Sheet1!C54="","",Sheet1!C54)</f>
         <v/>
       </c>
-      <c r="D54" s="5" t="str">
+      <c r="D54" s="6" t="str">
         <f aca="false">IF(Sheet1!D54="","",Sheet1!D54)</f>
         <v/>
       </c>
-      <c r="E54" s="5" t="str">
+      <c r="E54" s="6" t="str">
         <f aca="false">IF(Sheet1!E54="","",Sheet1!E54)</f>
         <v/>
       </c>
-      <c r="F54" s="5" t="str">
+      <c r="F54" s="6" t="str">
         <f aca="false">IF(Sheet1!F54="","",Sheet1!F54)</f>
         <v/>
       </c>
@@ -3093,30 +3097,30 @@
         <f aca="false">LEFT(F54,1)</f>
         <v/>
       </c>
-      <c r="I54" s="12"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I54" s="13"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="str">
         <f aca="false">IF(Sheet1!A55="","",Sheet1!A55)</f>
         <v/>
       </c>
-      <c r="B55" s="5" t="str">
+      <c r="B55" s="6" t="str">
         <f aca="false">IF(Sheet1!B55="","",Sheet1!B55)</f>
         <v/>
       </c>
-      <c r="C55" s="5" t="str">
+      <c r="C55" s="6" t="str">
         <f aca="false">IF(Sheet1!C55="","",Sheet1!C55)</f>
         <v/>
       </c>
-      <c r="D55" s="5" t="str">
+      <c r="D55" s="6" t="str">
         <f aca="false">IF(Sheet1!D55="","",Sheet1!D55)</f>
         <v/>
       </c>
-      <c r="E55" s="5" t="str">
+      <c r="E55" s="6" t="str">
         <f aca="false">IF(Sheet1!E55="","",Sheet1!E55)</f>
         <v/>
       </c>
-      <c r="F55" s="5" t="str">
+      <c r="F55" s="6" t="str">
         <f aca="false">IF(Sheet1!F55="","",Sheet1!F55)</f>
         <v/>
       </c>
@@ -3124,30 +3128,30 @@
         <f aca="false">LEFT(F55,1)</f>
         <v/>
       </c>
-      <c r="I55" s="12"/>
-    </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="13"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="str">
         <f aca="false">IF(Sheet1!A56="","",Sheet1!A56)</f>
         <v/>
       </c>
-      <c r="B56" s="5" t="str">
+      <c r="B56" s="6" t="str">
         <f aca="false">IF(Sheet1!B56="","",Sheet1!B56)</f>
         <v/>
       </c>
-      <c r="C56" s="5" t="str">
+      <c r="C56" s="6" t="str">
         <f aca="false">IF(Sheet1!C56="","",Sheet1!C56)</f>
         <v/>
       </c>
-      <c r="D56" s="5" t="str">
+      <c r="D56" s="6" t="str">
         <f aca="false">IF(Sheet1!D56="","",Sheet1!D56)</f>
         <v/>
       </c>
-      <c r="E56" s="5" t="str">
+      <c r="E56" s="6" t="str">
         <f aca="false">IF(Sheet1!E56="","",Sheet1!E56)</f>
         <v/>
       </c>
-      <c r="F56" s="5" t="str">
+      <c r="F56" s="6" t="str">
         <f aca="false">IF(Sheet1!F56="","",Sheet1!F56)</f>
         <v/>
       </c>
@@ -3155,30 +3159,30 @@
         <f aca="false">LEFT(F56,1)</f>
         <v/>
       </c>
-      <c r="I56" s="12"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="13"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="str">
         <f aca="false">IF(Sheet1!A57="","",Sheet1!A57)</f>
         <v/>
       </c>
-      <c r="B57" s="5" t="str">
+      <c r="B57" s="6" t="str">
         <f aca="false">IF(Sheet1!B57="","",Sheet1!B57)</f>
         <v/>
       </c>
-      <c r="C57" s="5" t="str">
+      <c r="C57" s="6" t="str">
         <f aca="false">IF(Sheet1!C57="","",Sheet1!C57)</f>
         <v/>
       </c>
-      <c r="D57" s="5" t="str">
+      <c r="D57" s="6" t="str">
         <f aca="false">IF(Sheet1!D57="","",Sheet1!D57)</f>
         <v/>
       </c>
-      <c r="E57" s="5" t="str">
+      <c r="E57" s="6" t="str">
         <f aca="false">IF(Sheet1!E57="","",Sheet1!E57)</f>
         <v/>
       </c>
-      <c r="F57" s="5" t="str">
+      <c r="F57" s="6" t="str">
         <f aca="false">IF(Sheet1!F57="","",Sheet1!F57)</f>
         <v/>
       </c>
@@ -3186,30 +3190,30 @@
         <f aca="false">LEFT(F57,1)</f>
         <v/>
       </c>
-      <c r="I57" s="12"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I57" s="13"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="str">
         <f aca="false">IF(Sheet1!A58="","",Sheet1!A58)</f>
         <v/>
       </c>
-      <c r="B58" s="5" t="str">
+      <c r="B58" s="6" t="str">
         <f aca="false">IF(Sheet1!B58="","",Sheet1!B58)</f>
         <v/>
       </c>
-      <c r="C58" s="5" t="str">
+      <c r="C58" s="6" t="str">
         <f aca="false">IF(Sheet1!C58="","",Sheet1!C58)</f>
         <v/>
       </c>
-      <c r="D58" s="5" t="str">
+      <c r="D58" s="6" t="str">
         <f aca="false">IF(Sheet1!D58="","",Sheet1!D58)</f>
         <v/>
       </c>
-      <c r="E58" s="5" t="str">
+      <c r="E58" s="6" t="str">
         <f aca="false">IF(Sheet1!E58="","",Sheet1!E58)</f>
         <v/>
       </c>
-      <c r="F58" s="5" t="str">
+      <c r="F58" s="6" t="str">
         <f aca="false">IF(Sheet1!F58="","",Sheet1!F58)</f>
         <v/>
       </c>
@@ -3217,30 +3221,30 @@
         <f aca="false">LEFT(F58,1)</f>
         <v/>
       </c>
-      <c r="I58" s="12"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="13"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="str">
         <f aca="false">IF(Sheet1!A59="","",Sheet1!A59)</f>
         <v/>
       </c>
-      <c r="B59" s="5" t="str">
+      <c r="B59" s="6" t="str">
         <f aca="false">IF(Sheet1!B59="","",Sheet1!B59)</f>
         <v/>
       </c>
-      <c r="C59" s="5" t="str">
+      <c r="C59" s="6" t="str">
         <f aca="false">IF(Sheet1!C59="","",Sheet1!C59)</f>
         <v/>
       </c>
-      <c r="D59" s="5" t="str">
+      <c r="D59" s="6" t="str">
         <f aca="false">IF(Sheet1!D59="","",Sheet1!D59)</f>
         <v/>
       </c>
-      <c r="E59" s="5" t="str">
+      <c r="E59" s="6" t="str">
         <f aca="false">IF(Sheet1!E59="","",Sheet1!E59)</f>
         <v/>
       </c>
-      <c r="F59" s="5" t="str">
+      <c r="F59" s="6" t="str">
         <f aca="false">IF(Sheet1!F59="","",Sheet1!F59)</f>
         <v/>
       </c>
@@ -3248,30 +3252,30 @@
         <f aca="false">LEFT(F59,1)</f>
         <v/>
       </c>
-      <c r="I59" s="12"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I59" s="13"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="str">
         <f aca="false">IF(Sheet1!A60="","",Sheet1!A60)</f>
         <v/>
       </c>
-      <c r="B60" s="5" t="str">
+      <c r="B60" s="6" t="str">
         <f aca="false">IF(Sheet1!B60="","",Sheet1!B60)</f>
         <v/>
       </c>
-      <c r="C60" s="5" t="str">
+      <c r="C60" s="6" t="str">
         <f aca="false">IF(Sheet1!C60="","",Sheet1!C60)</f>
         <v/>
       </c>
-      <c r="D60" s="5" t="str">
+      <c r="D60" s="6" t="str">
         <f aca="false">IF(Sheet1!D60="","",Sheet1!D60)</f>
         <v/>
       </c>
-      <c r="E60" s="5" t="str">
+      <c r="E60" s="6" t="str">
         <f aca="false">IF(Sheet1!E60="","",Sheet1!E60)</f>
         <v/>
       </c>
-      <c r="F60" s="5" t="str">
+      <c r="F60" s="6" t="str">
         <f aca="false">IF(Sheet1!F60="","",Sheet1!F60)</f>
         <v/>
       </c>
@@ -3279,30 +3283,30 @@
         <f aca="false">LEFT(F60,1)</f>
         <v/>
       </c>
-      <c r="I60" s="12"/>
-    </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="str">
         <f aca="false">IF(Sheet1!A61="","",Sheet1!A61)</f>
         <v/>
       </c>
-      <c r="B61" s="5" t="str">
+      <c r="B61" s="6" t="str">
         <f aca="false">IF(Sheet1!B61="","",Sheet1!B61)</f>
         <v/>
       </c>
-      <c r="C61" s="5" t="str">
+      <c r="C61" s="6" t="str">
         <f aca="false">IF(Sheet1!C61="","",Sheet1!C61)</f>
         <v/>
       </c>
-      <c r="D61" s="5" t="str">
+      <c r="D61" s="6" t="str">
         <f aca="false">IF(Sheet1!D61="","",Sheet1!D61)</f>
         <v/>
       </c>
-      <c r="E61" s="5" t="str">
+      <c r="E61" s="6" t="str">
         <f aca="false">IF(Sheet1!E61="","",Sheet1!E61)</f>
         <v/>
       </c>
-      <c r="F61" s="5" t="str">
+      <c r="F61" s="6" t="str">
         <f aca="false">IF(Sheet1!F61="","",Sheet1!F61)</f>
         <v/>
       </c>
@@ -3310,30 +3314,30 @@
         <f aca="false">LEFT(F61,1)</f>
         <v/>
       </c>
-      <c r="I61" s="12"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="13"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="str">
         <f aca="false">IF(Sheet1!A62="","",Sheet1!A62)</f>
         <v/>
       </c>
-      <c r="B62" s="5" t="str">
+      <c r="B62" s="6" t="str">
         <f aca="false">IF(Sheet1!B62="","",Sheet1!B62)</f>
         <v/>
       </c>
-      <c r="C62" s="5" t="str">
+      <c r="C62" s="6" t="str">
         <f aca="false">IF(Sheet1!C62="","",Sheet1!C62)</f>
         <v/>
       </c>
-      <c r="D62" s="5" t="str">
+      <c r="D62" s="6" t="str">
         <f aca="false">IF(Sheet1!D62="","",Sheet1!D62)</f>
         <v/>
       </c>
-      <c r="E62" s="5" t="str">
+      <c r="E62" s="6" t="str">
         <f aca="false">IF(Sheet1!E62="","",Sheet1!E62)</f>
         <v/>
       </c>
-      <c r="F62" s="5" t="str">
+      <c r="F62" s="6" t="str">
         <f aca="false">IF(Sheet1!F62="","",Sheet1!F62)</f>
         <v/>
       </c>
@@ -3341,30 +3345,30 @@
         <f aca="false">LEFT(F62,1)</f>
         <v/>
       </c>
-      <c r="I62" s="12"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="13"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="str">
         <f aca="false">IF(Sheet1!A63="","",Sheet1!A63)</f>
         <v/>
       </c>
-      <c r="B63" s="5" t="str">
+      <c r="B63" s="6" t="str">
         <f aca="false">IF(Sheet1!B63="","",Sheet1!B63)</f>
         <v/>
       </c>
-      <c r="C63" s="5" t="str">
+      <c r="C63" s="6" t="str">
         <f aca="false">IF(Sheet1!C63="","",Sheet1!C63)</f>
         <v/>
       </c>
-      <c r="D63" s="5" t="str">
+      <c r="D63" s="6" t="str">
         <f aca="false">IF(Sheet1!D63="","",Sheet1!D63)</f>
         <v/>
       </c>
-      <c r="E63" s="5" t="str">
+      <c r="E63" s="6" t="str">
         <f aca="false">IF(Sheet1!E63="","",Sheet1!E63)</f>
         <v/>
       </c>
-      <c r="F63" s="5" t="str">
+      <c r="F63" s="6" t="str">
         <f aca="false">IF(Sheet1!F63="","",Sheet1!F63)</f>
         <v/>
       </c>
@@ -3372,30 +3376,30 @@
         <f aca="false">LEFT(F63,1)</f>
         <v/>
       </c>
-      <c r="I63" s="12"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I63" s="13"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="str">
         <f aca="false">IF(Sheet1!A64="","",Sheet1!A64)</f>
         <v/>
       </c>
-      <c r="B64" s="5" t="str">
+      <c r="B64" s="6" t="str">
         <f aca="false">IF(Sheet1!B64="","",Sheet1!B64)</f>
         <v/>
       </c>
-      <c r="C64" s="5" t="str">
+      <c r="C64" s="6" t="str">
         <f aca="false">IF(Sheet1!C64="","",Sheet1!C64)</f>
         <v/>
       </c>
-      <c r="D64" s="5" t="str">
+      <c r="D64" s="6" t="str">
         <f aca="false">IF(Sheet1!D64="","",Sheet1!D64)</f>
         <v/>
       </c>
-      <c r="E64" s="5" t="str">
+      <c r="E64" s="6" t="str">
         <f aca="false">IF(Sheet1!E64="","",Sheet1!E64)</f>
         <v/>
       </c>
-      <c r="F64" s="5" t="str">
+      <c r="F64" s="6" t="str">
         <f aca="false">IF(Sheet1!F64="","",Sheet1!F64)</f>
         <v/>
       </c>
@@ -3403,30 +3407,30 @@
         <f aca="false">LEFT(F64,1)</f>
         <v/>
       </c>
-      <c r="I64" s="12"/>
-    </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I64" s="13"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="str">
         <f aca="false">IF(Sheet1!A65="","",Sheet1!A65)</f>
         <v/>
       </c>
-      <c r="B65" s="5" t="str">
+      <c r="B65" s="6" t="str">
         <f aca="false">IF(Sheet1!B65="","",Sheet1!B65)</f>
         <v/>
       </c>
-      <c r="C65" s="5" t="str">
+      <c r="C65" s="6" t="str">
         <f aca="false">IF(Sheet1!C65="","",Sheet1!C65)</f>
         <v/>
       </c>
-      <c r="D65" s="5" t="str">
+      <c r="D65" s="6" t="str">
         <f aca="false">IF(Sheet1!D65="","",Sheet1!D65)</f>
         <v/>
       </c>
-      <c r="E65" s="5" t="str">
+      <c r="E65" s="6" t="str">
         <f aca="false">IF(Sheet1!E65="","",Sheet1!E65)</f>
         <v/>
       </c>
-      <c r="F65" s="5" t="str">
+      <c r="F65" s="6" t="str">
         <f aca="false">IF(Sheet1!F65="","",Sheet1!F65)</f>
         <v/>
       </c>
@@ -3434,30 +3438,30 @@
         <f aca="false">LEFT(F65,1)</f>
         <v/>
       </c>
-      <c r="I65" s="12"/>
-    </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="13"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="str">
         <f aca="false">IF(Sheet1!A66="","",Sheet1!A66)</f>
         <v/>
       </c>
-      <c r="B66" s="5" t="str">
+      <c r="B66" s="6" t="str">
         <f aca="false">IF(Sheet1!B66="","",Sheet1!B66)</f>
         <v/>
       </c>
-      <c r="C66" s="5" t="str">
+      <c r="C66" s="6" t="str">
         <f aca="false">IF(Sheet1!C66="","",Sheet1!C66)</f>
         <v/>
       </c>
-      <c r="D66" s="5" t="str">
+      <c r="D66" s="6" t="str">
         <f aca="false">IF(Sheet1!D66="","",Sheet1!D66)</f>
         <v/>
       </c>
-      <c r="E66" s="5" t="str">
+      <c r="E66" s="6" t="str">
         <f aca="false">IF(Sheet1!E66="","",Sheet1!E66)</f>
         <v/>
       </c>
-      <c r="F66" s="5" t="str">
+      <c r="F66" s="6" t="str">
         <f aca="false">IF(Sheet1!F66="","",Sheet1!F66)</f>
         <v/>
       </c>
@@ -3465,30 +3469,30 @@
         <f aca="false">LEFT(F66,1)</f>
         <v/>
       </c>
-      <c r="I66" s="12"/>
-    </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="13"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="str">
         <f aca="false">IF(Sheet1!A67="","",Sheet1!A67)</f>
         <v/>
       </c>
-      <c r="B67" s="5" t="str">
+      <c r="B67" s="6" t="str">
         <f aca="false">IF(Sheet1!B67="","",Sheet1!B67)</f>
         <v/>
       </c>
-      <c r="C67" s="5" t="str">
+      <c r="C67" s="6" t="str">
         <f aca="false">IF(Sheet1!C67="","",Sheet1!C67)</f>
         <v/>
       </c>
-      <c r="D67" s="5" t="str">
+      <c r="D67" s="6" t="str">
         <f aca="false">IF(Sheet1!D67="","",Sheet1!D67)</f>
         <v/>
       </c>
-      <c r="E67" s="5" t="str">
+      <c r="E67" s="6" t="str">
         <f aca="false">IF(Sheet1!E67="","",Sheet1!E67)</f>
         <v/>
       </c>
-      <c r="F67" s="5" t="str">
+      <c r="F67" s="6" t="str">
         <f aca="false">IF(Sheet1!F67="","",Sheet1!F67)</f>
         <v/>
       </c>
@@ -3496,30 +3500,30 @@
         <f aca="false">LEFT(F67,1)</f>
         <v/>
       </c>
-      <c r="I67" s="12"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="13"/>
+    </row>
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="str">
         <f aca="false">IF(Sheet1!A68="","",Sheet1!A68)</f>
         <v/>
       </c>
-      <c r="B68" s="5" t="str">
+      <c r="B68" s="6" t="str">
         <f aca="false">IF(Sheet1!B68="","",Sheet1!B68)</f>
         <v/>
       </c>
-      <c r="C68" s="5" t="str">
+      <c r="C68" s="6" t="str">
         <f aca="false">IF(Sheet1!C68="","",Sheet1!C68)</f>
         <v/>
       </c>
-      <c r="D68" s="5" t="str">
+      <c r="D68" s="6" t="str">
         <f aca="false">IF(Sheet1!D68="","",Sheet1!D68)</f>
         <v/>
       </c>
-      <c r="E68" s="5" t="str">
+      <c r="E68" s="6" t="str">
         <f aca="false">IF(Sheet1!E68="","",Sheet1!E68)</f>
         <v/>
       </c>
-      <c r="F68" s="5" t="str">
+      <c r="F68" s="6" t="str">
         <f aca="false">IF(Sheet1!F68="","",Sheet1!F68)</f>
         <v/>
       </c>
@@ -3527,30 +3531,30 @@
         <f aca="false">LEFT(F68,1)</f>
         <v/>
       </c>
-      <c r="I68" s="12"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I68" s="13"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="str">
         <f aca="false">IF(Sheet1!A69="","",Sheet1!A69)</f>
         <v/>
       </c>
-      <c r="B69" s="5" t="str">
+      <c r="B69" s="6" t="str">
         <f aca="false">IF(Sheet1!B69="","",Sheet1!B69)</f>
         <v/>
       </c>
-      <c r="C69" s="5" t="str">
+      <c r="C69" s="6" t="str">
         <f aca="false">IF(Sheet1!C69="","",Sheet1!C69)</f>
         <v/>
       </c>
-      <c r="D69" s="5" t="str">
+      <c r="D69" s="6" t="str">
         <f aca="false">IF(Sheet1!D69="","",Sheet1!D69)</f>
         <v/>
       </c>
-      <c r="E69" s="5" t="str">
+      <c r="E69" s="6" t="str">
         <f aca="false">IF(Sheet1!E69="","",Sheet1!E69)</f>
         <v/>
       </c>
-      <c r="F69" s="5" t="str">
+      <c r="F69" s="6" t="str">
         <f aca="false">IF(Sheet1!F69="","",Sheet1!F69)</f>
         <v/>
       </c>
@@ -3558,30 +3562,30 @@
         <f aca="false">LEFT(F69,1)</f>
         <v/>
       </c>
-      <c r="I69" s="12"/>
-    </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I69" s="13"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="str">
         <f aca="false">IF(Sheet1!A70="","",Sheet1!A70)</f>
         <v/>
       </c>
-      <c r="B70" s="5" t="str">
+      <c r="B70" s="6" t="str">
         <f aca="false">IF(Sheet1!B70="","",Sheet1!B70)</f>
         <v/>
       </c>
-      <c r="C70" s="5" t="str">
+      <c r="C70" s="6" t="str">
         <f aca="false">IF(Sheet1!C70="","",Sheet1!C70)</f>
         <v/>
       </c>
-      <c r="D70" s="5" t="str">
+      <c r="D70" s="6" t="str">
         <f aca="false">IF(Sheet1!D70="","",Sheet1!D70)</f>
         <v/>
       </c>
-      <c r="E70" s="5" t="str">
+      <c r="E70" s="6" t="str">
         <f aca="false">IF(Sheet1!E70="","",Sheet1!E70)</f>
         <v/>
       </c>
-      <c r="F70" s="5" t="str">
+      <c r="F70" s="6" t="str">
         <f aca="false">IF(Sheet1!F70="","",Sheet1!F70)</f>
         <v/>
       </c>
@@ -3589,30 +3593,30 @@
         <f aca="false">LEFT(F70,1)</f>
         <v/>
       </c>
-      <c r="I70" s="12"/>
-    </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I70" s="13"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="str">
         <f aca="false">IF(Sheet1!A71="","",Sheet1!A71)</f>
         <v/>
       </c>
-      <c r="B71" s="5" t="str">
+      <c r="B71" s="6" t="str">
         <f aca="false">IF(Sheet1!B71="","",Sheet1!B71)</f>
         <v/>
       </c>
-      <c r="C71" s="5" t="str">
+      <c r="C71" s="6" t="str">
         <f aca="false">IF(Sheet1!C71="","",Sheet1!C71)</f>
         <v/>
       </c>
-      <c r="D71" s="5" t="str">
+      <c r="D71" s="6" t="str">
         <f aca="false">IF(Sheet1!D71="","",Sheet1!D71)</f>
         <v/>
       </c>
-      <c r="E71" s="5" t="str">
+      <c r="E71" s="6" t="str">
         <f aca="false">IF(Sheet1!E71="","",Sheet1!E71)</f>
         <v/>
       </c>
-      <c r="F71" s="5" t="str">
+      <c r="F71" s="6" t="str">
         <f aca="false">IF(Sheet1!F71="","",Sheet1!F71)</f>
         <v/>
       </c>
@@ -3620,30 +3624,30 @@
         <f aca="false">LEFT(F71,1)</f>
         <v/>
       </c>
-      <c r="I71" s="12"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I71" s="13"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="str">
         <f aca="false">IF(Sheet1!A72="","",Sheet1!A72)</f>
         <v/>
       </c>
-      <c r="B72" s="5" t="str">
+      <c r="B72" s="6" t="str">
         <f aca="false">IF(Sheet1!B72="","",Sheet1!B72)</f>
         <v/>
       </c>
-      <c r="C72" s="5" t="str">
+      <c r="C72" s="6" t="str">
         <f aca="false">IF(Sheet1!C72="","",Sheet1!C72)</f>
         <v/>
       </c>
-      <c r="D72" s="5" t="str">
+      <c r="D72" s="6" t="str">
         <f aca="false">IF(Sheet1!D72="","",Sheet1!D72)</f>
         <v/>
       </c>
-      <c r="E72" s="5" t="str">
+      <c r="E72" s="6" t="str">
         <f aca="false">IF(Sheet1!E72="","",Sheet1!E72)</f>
         <v/>
       </c>
-      <c r="F72" s="5" t="str">
+      <c r="F72" s="6" t="str">
         <f aca="false">IF(Sheet1!F72="","",Sheet1!F72)</f>
         <v/>
       </c>
@@ -3651,30 +3655,30 @@
         <f aca="false">LEFT(F72,1)</f>
         <v/>
       </c>
-      <c r="I72" s="12"/>
-    </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I72" s="13"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="str">
         <f aca="false">IF(Sheet1!A73="","",Sheet1!A73)</f>
         <v/>
       </c>
-      <c r="B73" s="5" t="str">
+      <c r="B73" s="6" t="str">
         <f aca="false">IF(Sheet1!B73="","",Sheet1!B73)</f>
         <v/>
       </c>
-      <c r="C73" s="5" t="str">
+      <c r="C73" s="6" t="str">
         <f aca="false">IF(Sheet1!C73="","",Sheet1!C73)</f>
         <v/>
       </c>
-      <c r="D73" s="5" t="str">
+      <c r="D73" s="6" t="str">
         <f aca="false">IF(Sheet1!D73="","",Sheet1!D73)</f>
         <v/>
       </c>
-      <c r="E73" s="5" t="str">
+      <c r="E73" s="6" t="str">
         <f aca="false">IF(Sheet1!E73="","",Sheet1!E73)</f>
         <v/>
       </c>
-      <c r="F73" s="5" t="str">
+      <c r="F73" s="6" t="str">
         <f aca="false">IF(Sheet1!F73="","",Sheet1!F73)</f>
         <v/>
       </c>
@@ -3682,30 +3686,30 @@
         <f aca="false">LEFT(F73,1)</f>
         <v/>
       </c>
-      <c r="I73" s="12"/>
-    </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I73" s="13"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="str">
         <f aca="false">IF(Sheet1!A74="","",Sheet1!A74)</f>
         <v/>
       </c>
-      <c r="B74" s="5" t="str">
+      <c r="B74" s="6" t="str">
         <f aca="false">IF(Sheet1!B74="","",Sheet1!B74)</f>
         <v/>
       </c>
-      <c r="C74" s="5" t="str">
+      <c r="C74" s="6" t="str">
         <f aca="false">IF(Sheet1!C74="","",Sheet1!C74)</f>
         <v/>
       </c>
-      <c r="D74" s="5" t="str">
+      <c r="D74" s="6" t="str">
         <f aca="false">IF(Sheet1!D74="","",Sheet1!D74)</f>
         <v/>
       </c>
-      <c r="E74" s="5" t="str">
+      <c r="E74" s="6" t="str">
         <f aca="false">IF(Sheet1!E74="","",Sheet1!E74)</f>
         <v/>
       </c>
-      <c r="F74" s="5" t="str">
+      <c r="F74" s="6" t="str">
         <f aca="false">IF(Sheet1!F74="","",Sheet1!F74)</f>
         <v/>
       </c>
@@ -3713,30 +3717,30 @@
         <f aca="false">LEFT(F74,1)</f>
         <v/>
       </c>
-      <c r="I74" s="12"/>
-    </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I74" s="13"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="str">
         <f aca="false">IF(Sheet1!A75="","",Sheet1!A75)</f>
         <v/>
       </c>
-      <c r="B75" s="5" t="str">
+      <c r="B75" s="6" t="str">
         <f aca="false">IF(Sheet1!B75="","",Sheet1!B75)</f>
         <v/>
       </c>
-      <c r="C75" s="5" t="str">
+      <c r="C75" s="6" t="str">
         <f aca="false">IF(Sheet1!C75="","",Sheet1!C75)</f>
         <v/>
       </c>
-      <c r="D75" s="5" t="str">
+      <c r="D75" s="6" t="str">
         <f aca="false">IF(Sheet1!D75="","",Sheet1!D75)</f>
         <v/>
       </c>
-      <c r="E75" s="5" t="str">
+      <c r="E75" s="6" t="str">
         <f aca="false">IF(Sheet1!E75="","",Sheet1!E75)</f>
         <v/>
       </c>
-      <c r="F75" s="5" t="str">
+      <c r="F75" s="6" t="str">
         <f aca="false">IF(Sheet1!F75="","",Sheet1!F75)</f>
         <v/>
       </c>
@@ -3744,30 +3748,30 @@
         <f aca="false">LEFT(F75,1)</f>
         <v/>
       </c>
-      <c r="I75" s="12"/>
-    </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="13"/>
+    </row>
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="str">
         <f aca="false">IF(Sheet1!A76="","",Sheet1!A76)</f>
         <v/>
       </c>
-      <c r="B76" s="5" t="str">
+      <c r="B76" s="6" t="str">
         <f aca="false">IF(Sheet1!B76="","",Sheet1!B76)</f>
         <v/>
       </c>
-      <c r="C76" s="5" t="str">
+      <c r="C76" s="6" t="str">
         <f aca="false">IF(Sheet1!C76="","",Sheet1!C76)</f>
         <v/>
       </c>
-      <c r="D76" s="5" t="str">
+      <c r="D76" s="6" t="str">
         <f aca="false">IF(Sheet1!D76="","",Sheet1!D76)</f>
         <v/>
       </c>
-      <c r="E76" s="5" t="str">
+      <c r="E76" s="6" t="str">
         <f aca="false">IF(Sheet1!E76="","",Sheet1!E76)</f>
         <v/>
       </c>
-      <c r="F76" s="5" t="str">
+      <c r="F76" s="6" t="str">
         <f aca="false">IF(Sheet1!F76="","",Sheet1!F76)</f>
         <v/>
       </c>
@@ -3775,30 +3779,30 @@
         <f aca="false">LEFT(F76,1)</f>
         <v/>
       </c>
-      <c r="I76" s="12"/>
-    </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I76" s="13"/>
+    </row>
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="str">
         <f aca="false">IF(Sheet1!A77="","",Sheet1!A77)</f>
         <v/>
       </c>
-      <c r="B77" s="5" t="str">
+      <c r="B77" s="6" t="str">
         <f aca="false">IF(Sheet1!B77="","",Sheet1!B77)</f>
         <v/>
       </c>
-      <c r="C77" s="5" t="str">
+      <c r="C77" s="6" t="str">
         <f aca="false">IF(Sheet1!C77="","",Sheet1!C77)</f>
         <v/>
       </c>
-      <c r="D77" s="5" t="str">
+      <c r="D77" s="6" t="str">
         <f aca="false">IF(Sheet1!D77="","",Sheet1!D77)</f>
         <v/>
       </c>
-      <c r="E77" s="5" t="str">
+      <c r="E77" s="6" t="str">
         <f aca="false">IF(Sheet1!E77="","",Sheet1!E77)</f>
         <v/>
       </c>
-      <c r="F77" s="5" t="str">
+      <c r="F77" s="6" t="str">
         <f aca="false">IF(Sheet1!F77="","",Sheet1!F77)</f>
         <v/>
       </c>
@@ -3806,30 +3810,30 @@
         <f aca="false">LEFT(F77,1)</f>
         <v/>
       </c>
-      <c r="I77" s="12"/>
-    </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I77" s="13"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="str">
         <f aca="false">IF(Sheet1!A78="","",Sheet1!A78)</f>
         <v/>
       </c>
-      <c r="B78" s="5" t="str">
+      <c r="B78" s="6" t="str">
         <f aca="false">IF(Sheet1!B78="","",Sheet1!B78)</f>
         <v/>
       </c>
-      <c r="C78" s="5" t="str">
+      <c r="C78" s="6" t="str">
         <f aca="false">IF(Sheet1!C78="","",Sheet1!C78)</f>
         <v/>
       </c>
-      <c r="D78" s="5" t="str">
+      <c r="D78" s="6" t="str">
         <f aca="false">IF(Sheet1!D78="","",Sheet1!D78)</f>
         <v/>
       </c>
-      <c r="E78" s="5" t="str">
+      <c r="E78" s="6" t="str">
         <f aca="false">IF(Sheet1!E78="","",Sheet1!E78)</f>
         <v/>
       </c>
-      <c r="F78" s="5" t="str">
+      <c r="F78" s="6" t="str">
         <f aca="false">IF(Sheet1!F78="","",Sheet1!F78)</f>
         <v/>
       </c>
@@ -3837,30 +3841,30 @@
         <f aca="false">LEFT(F78,1)</f>
         <v/>
       </c>
-      <c r="I78" s="12"/>
-    </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="13"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="str">
         <f aca="false">IF(Sheet1!A79="","",Sheet1!A79)</f>
         <v/>
       </c>
-      <c r="B79" s="5" t="str">
+      <c r="B79" s="6" t="str">
         <f aca="false">IF(Sheet1!B79="","",Sheet1!B79)</f>
         <v/>
       </c>
-      <c r="C79" s="5" t="str">
+      <c r="C79" s="6" t="str">
         <f aca="false">IF(Sheet1!C79="","",Sheet1!C79)</f>
         <v/>
       </c>
-      <c r="D79" s="5" t="str">
+      <c r="D79" s="6" t="str">
         <f aca="false">IF(Sheet1!D79="","",Sheet1!D79)</f>
         <v/>
       </c>
-      <c r="E79" s="5" t="str">
+      <c r="E79" s="6" t="str">
         <f aca="false">IF(Sheet1!E79="","",Sheet1!E79)</f>
         <v/>
       </c>
-      <c r="F79" s="5" t="str">
+      <c r="F79" s="6" t="str">
         <f aca="false">IF(Sheet1!F79="","",Sheet1!F79)</f>
         <v/>
       </c>
@@ -3868,30 +3872,30 @@
         <f aca="false">LEFT(F79,1)</f>
         <v/>
       </c>
-      <c r="I79" s="12"/>
-    </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I79" s="13"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="str">
         <f aca="false">IF(Sheet1!A80="","",Sheet1!A80)</f>
         <v/>
       </c>
-      <c r="B80" s="5" t="str">
+      <c r="B80" s="6" t="str">
         <f aca="false">IF(Sheet1!B80="","",Sheet1!B80)</f>
         <v/>
       </c>
-      <c r="C80" s="5" t="str">
+      <c r="C80" s="6" t="str">
         <f aca="false">IF(Sheet1!C80="","",Sheet1!C80)</f>
         <v/>
       </c>
-      <c r="D80" s="5" t="str">
+      <c r="D80" s="6" t="str">
         <f aca="false">IF(Sheet1!D80="","",Sheet1!D80)</f>
         <v/>
       </c>
-      <c r="E80" s="5" t="str">
+      <c r="E80" s="6" t="str">
         <f aca="false">IF(Sheet1!E80="","",Sheet1!E80)</f>
         <v/>
       </c>
-      <c r="F80" s="5" t="str">
+      <c r="F80" s="6" t="str">
         <f aca="false">IF(Sheet1!F80="","",Sheet1!F80)</f>
         <v/>
       </c>
@@ -3899,30 +3903,30 @@
         <f aca="false">LEFT(F80,1)</f>
         <v/>
       </c>
-      <c r="I80" s="12"/>
-    </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I80" s="13"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="str">
         <f aca="false">IF(Sheet1!A81="","",Sheet1!A81)</f>
         <v/>
       </c>
-      <c r="B81" s="5" t="str">
+      <c r="B81" s="6" t="str">
         <f aca="false">IF(Sheet1!B81="","",Sheet1!B81)</f>
         <v/>
       </c>
-      <c r="C81" s="5" t="str">
+      <c r="C81" s="6" t="str">
         <f aca="false">IF(Sheet1!C81="","",Sheet1!C81)</f>
         <v/>
       </c>
-      <c r="D81" s="5" t="str">
+      <c r="D81" s="6" t="str">
         <f aca="false">IF(Sheet1!D81="","",Sheet1!D81)</f>
         <v/>
       </c>
-      <c r="E81" s="5" t="str">
+      <c r="E81" s="6" t="str">
         <f aca="false">IF(Sheet1!E81="","",Sheet1!E81)</f>
         <v/>
       </c>
-      <c r="F81" s="5" t="str">
+      <c r="F81" s="6" t="str">
         <f aca="false">IF(Sheet1!F81="","",Sheet1!F81)</f>
         <v/>
       </c>
@@ -3930,30 +3934,30 @@
         <f aca="false">LEFT(F81,1)</f>
         <v/>
       </c>
-      <c r="I81" s="12"/>
-    </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I81" s="13"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="str">
         <f aca="false">IF(Sheet1!A82="","",Sheet1!A82)</f>
         <v/>
       </c>
-      <c r="B82" s="5" t="str">
+      <c r="B82" s="6" t="str">
         <f aca="false">IF(Sheet1!B82="","",Sheet1!B82)</f>
         <v/>
       </c>
-      <c r="C82" s="5" t="str">
+      <c r="C82" s="6" t="str">
         <f aca="false">IF(Sheet1!C82="","",Sheet1!C82)</f>
         <v/>
       </c>
-      <c r="D82" s="5" t="str">
+      <c r="D82" s="6" t="str">
         <f aca="false">IF(Sheet1!D82="","",Sheet1!D82)</f>
         <v/>
       </c>
-      <c r="E82" s="5" t="str">
+      <c r="E82" s="6" t="str">
         <f aca="false">IF(Sheet1!E82="","",Sheet1!E82)</f>
         <v/>
       </c>
-      <c r="F82" s="5" t="str">
+      <c r="F82" s="6" t="str">
         <f aca="false">IF(Sheet1!F82="","",Sheet1!F82)</f>
         <v/>
       </c>
@@ -3961,30 +3965,30 @@
         <f aca="false">LEFT(F82,1)</f>
         <v/>
       </c>
-      <c r="I82" s="12"/>
-    </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I82" s="13"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="str">
         <f aca="false">IF(Sheet1!A83="","",Sheet1!A83)</f>
         <v/>
       </c>
-      <c r="B83" s="5" t="str">
+      <c r="B83" s="6" t="str">
         <f aca="false">IF(Sheet1!B83="","",Sheet1!B83)</f>
         <v/>
       </c>
-      <c r="C83" s="5" t="str">
+      <c r="C83" s="6" t="str">
         <f aca="false">IF(Sheet1!C83="","",Sheet1!C83)</f>
         <v/>
       </c>
-      <c r="D83" s="5" t="str">
+      <c r="D83" s="6" t="str">
         <f aca="false">IF(Sheet1!D83="","",Sheet1!D83)</f>
         <v/>
       </c>
-      <c r="E83" s="5" t="str">
+      <c r="E83" s="6" t="str">
         <f aca="false">IF(Sheet1!E83="","",Sheet1!E83)</f>
         <v/>
       </c>
-      <c r="F83" s="5" t="str">
+      <c r="F83" s="6" t="str">
         <f aca="false">IF(Sheet1!F83="","",Sheet1!F83)</f>
         <v/>
       </c>
@@ -3992,30 +3996,30 @@
         <f aca="false">LEFT(F83,1)</f>
         <v/>
       </c>
-      <c r="I83" s="12"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="13"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="str">
         <f aca="false">IF(Sheet1!A84="","",Sheet1!A84)</f>
         <v/>
       </c>
-      <c r="B84" s="5" t="str">
+      <c r="B84" s="6" t="str">
         <f aca="false">IF(Sheet1!B84="","",Sheet1!B84)</f>
         <v/>
       </c>
-      <c r="C84" s="5" t="str">
+      <c r="C84" s="6" t="str">
         <f aca="false">IF(Sheet1!C84="","",Sheet1!C84)</f>
         <v/>
       </c>
-      <c r="D84" s="5" t="str">
+      <c r="D84" s="6" t="str">
         <f aca="false">IF(Sheet1!D84="","",Sheet1!D84)</f>
         <v/>
       </c>
-      <c r="E84" s="5" t="str">
+      <c r="E84" s="6" t="str">
         <f aca="false">IF(Sheet1!E84="","",Sheet1!E84)</f>
         <v/>
       </c>
-      <c r="F84" s="5" t="str">
+      <c r="F84" s="6" t="str">
         <f aca="false">IF(Sheet1!F84="","",Sheet1!F84)</f>
         <v/>
       </c>
@@ -4023,30 +4027,30 @@
         <f aca="false">LEFT(F84,1)</f>
         <v/>
       </c>
-      <c r="I84" s="12"/>
-    </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="13"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="str">
         <f aca="false">IF(Sheet1!A85="","",Sheet1!A85)</f>
         <v/>
       </c>
-      <c r="B85" s="5" t="str">
+      <c r="B85" s="6" t="str">
         <f aca="false">IF(Sheet1!B85="","",Sheet1!B85)</f>
         <v/>
       </c>
-      <c r="C85" s="5" t="str">
+      <c r="C85" s="6" t="str">
         <f aca="false">IF(Sheet1!C85="","",Sheet1!C85)</f>
         <v/>
       </c>
-      <c r="D85" s="5" t="str">
+      <c r="D85" s="6" t="str">
         <f aca="false">IF(Sheet1!D85="","",Sheet1!D85)</f>
         <v/>
       </c>
-      <c r="E85" s="5" t="str">
+      <c r="E85" s="6" t="str">
         <f aca="false">IF(Sheet1!E85="","",Sheet1!E85)</f>
         <v/>
       </c>
-      <c r="F85" s="5" t="str">
+      <c r="F85" s="6" t="str">
         <f aca="false">IF(Sheet1!F85="","",Sheet1!F85)</f>
         <v/>
       </c>
@@ -4054,30 +4058,30 @@
         <f aca="false">LEFT(F85,1)</f>
         <v/>
       </c>
-      <c r="I85" s="12"/>
-    </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I85" s="13"/>
+    </row>
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="str">
         <f aca="false">IF(Sheet1!A86="","",Sheet1!A86)</f>
         <v/>
       </c>
-      <c r="B86" s="5" t="str">
+      <c r="B86" s="6" t="str">
         <f aca="false">IF(Sheet1!B86="","",Sheet1!B86)</f>
         <v/>
       </c>
-      <c r="C86" s="5" t="str">
+      <c r="C86" s="6" t="str">
         <f aca="false">IF(Sheet1!C86="","",Sheet1!C86)</f>
         <v/>
       </c>
-      <c r="D86" s="5" t="str">
+      <c r="D86" s="6" t="str">
         <f aca="false">IF(Sheet1!D86="","",Sheet1!D86)</f>
         <v/>
       </c>
-      <c r="E86" s="5" t="str">
+      <c r="E86" s="6" t="str">
         <f aca="false">IF(Sheet1!E86="","",Sheet1!E86)</f>
         <v/>
       </c>
-      <c r="F86" s="5" t="str">
+      <c r="F86" s="6" t="str">
         <f aca="false">IF(Sheet1!F86="","",Sheet1!F86)</f>
         <v/>
       </c>
@@ -4085,30 +4089,30 @@
         <f aca="false">LEFT(F86,1)</f>
         <v/>
       </c>
-      <c r="I86" s="12"/>
-    </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I86" s="13"/>
+    </row>
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="str">
         <f aca="false">IF(Sheet1!A87="","",Sheet1!A87)</f>
         <v/>
       </c>
-      <c r="B87" s="5" t="str">
+      <c r="B87" s="6" t="str">
         <f aca="false">IF(Sheet1!B87="","",Sheet1!B87)</f>
         <v/>
       </c>
-      <c r="C87" s="5" t="str">
+      <c r="C87" s="6" t="str">
         <f aca="false">IF(Sheet1!C87="","",Sheet1!C87)</f>
         <v/>
       </c>
-      <c r="D87" s="5" t="str">
+      <c r="D87" s="6" t="str">
         <f aca="false">IF(Sheet1!D87="","",Sheet1!D87)</f>
         <v/>
       </c>
-      <c r="E87" s="5" t="str">
+      <c r="E87" s="6" t="str">
         <f aca="false">IF(Sheet1!E87="","",Sheet1!E87)</f>
         <v/>
       </c>
-      <c r="F87" s="5" t="str">
+      <c r="F87" s="6" t="str">
         <f aca="false">IF(Sheet1!F87="","",Sheet1!F87)</f>
         <v/>
       </c>
@@ -4116,30 +4120,30 @@
         <f aca="false">LEFT(F87,1)</f>
         <v/>
       </c>
-      <c r="I87" s="12"/>
-    </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I87" s="13"/>
+    </row>
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="str">
         <f aca="false">IF(Sheet1!A88="","",Sheet1!A88)</f>
         <v/>
       </c>
-      <c r="B88" s="5" t="str">
+      <c r="B88" s="6" t="str">
         <f aca="false">IF(Sheet1!B88="","",Sheet1!B88)</f>
         <v/>
       </c>
-      <c r="C88" s="5" t="str">
+      <c r="C88" s="6" t="str">
         <f aca="false">IF(Sheet1!C88="","",Sheet1!C88)</f>
         <v/>
       </c>
-      <c r="D88" s="5" t="str">
+      <c r="D88" s="6" t="str">
         <f aca="false">IF(Sheet1!D88="","",Sheet1!D88)</f>
         <v/>
       </c>
-      <c r="E88" s="5" t="str">
+      <c r="E88" s="6" t="str">
         <f aca="false">IF(Sheet1!E88="","",Sheet1!E88)</f>
         <v/>
       </c>
-      <c r="F88" s="5" t="str">
+      <c r="F88" s="6" t="str">
         <f aca="false">IF(Sheet1!F88="","",Sheet1!F88)</f>
         <v/>
       </c>
@@ -4147,30 +4151,30 @@
         <f aca="false">LEFT(F88,1)</f>
         <v/>
       </c>
-      <c r="I88" s="12"/>
-    </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I88" s="13"/>
+    </row>
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="str">
         <f aca="false">IF(Sheet1!A89="","",Sheet1!A89)</f>
         <v/>
       </c>
-      <c r="B89" s="5" t="str">
+      <c r="B89" s="6" t="str">
         <f aca="false">IF(Sheet1!B89="","",Sheet1!B89)</f>
         <v/>
       </c>
-      <c r="C89" s="5" t="str">
+      <c r="C89" s="6" t="str">
         <f aca="false">IF(Sheet1!C89="","",Sheet1!C89)</f>
         <v/>
       </c>
-      <c r="D89" s="5" t="str">
+      <c r="D89" s="6" t="str">
         <f aca="false">IF(Sheet1!D89="","",Sheet1!D89)</f>
         <v/>
       </c>
-      <c r="E89" s="5" t="str">
+      <c r="E89" s="6" t="str">
         <f aca="false">IF(Sheet1!E89="","",Sheet1!E89)</f>
         <v/>
       </c>
-      <c r="F89" s="5" t="str">
+      <c r="F89" s="6" t="str">
         <f aca="false">IF(Sheet1!F89="","",Sheet1!F89)</f>
         <v/>
       </c>
@@ -4178,30 +4182,30 @@
         <f aca="false">LEFT(F89,1)</f>
         <v/>
       </c>
-      <c r="I89" s="12"/>
-    </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I89" s="13"/>
+    </row>
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="str">
         <f aca="false">IF(Sheet1!A90="","",Sheet1!A90)</f>
         <v/>
       </c>
-      <c r="B90" s="5" t="str">
+      <c r="B90" s="6" t="str">
         <f aca="false">IF(Sheet1!B90="","",Sheet1!B90)</f>
         <v/>
       </c>
-      <c r="C90" s="5" t="str">
+      <c r="C90" s="6" t="str">
         <f aca="false">IF(Sheet1!C90="","",Sheet1!C90)</f>
         <v/>
       </c>
-      <c r="D90" s="5" t="str">
+      <c r="D90" s="6" t="str">
         <f aca="false">IF(Sheet1!D90="","",Sheet1!D90)</f>
         <v/>
       </c>
-      <c r="E90" s="5" t="str">
+      <c r="E90" s="6" t="str">
         <f aca="false">IF(Sheet1!E90="","",Sheet1!E90)</f>
         <v/>
       </c>
-      <c r="F90" s="5" t="str">
+      <c r="F90" s="6" t="str">
         <f aca="false">IF(Sheet1!F90="","",Sheet1!F90)</f>
         <v/>
       </c>
@@ -4209,30 +4213,30 @@
         <f aca="false">LEFT(F90,1)</f>
         <v/>
       </c>
-      <c r="I90" s="12"/>
-    </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I90" s="13"/>
+    </row>
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="str">
         <f aca="false">IF(Sheet1!A91="","",Sheet1!A91)</f>
         <v/>
       </c>
-      <c r="B91" s="5" t="str">
+      <c r="B91" s="6" t="str">
         <f aca="false">IF(Sheet1!B91="","",Sheet1!B91)</f>
         <v/>
       </c>
-      <c r="C91" s="5" t="str">
+      <c r="C91" s="6" t="str">
         <f aca="false">IF(Sheet1!C91="","",Sheet1!C91)</f>
         <v/>
       </c>
-      <c r="D91" s="5" t="str">
+      <c r="D91" s="6" t="str">
         <f aca="false">IF(Sheet1!D91="","",Sheet1!D91)</f>
         <v/>
       </c>
-      <c r="E91" s="5" t="str">
+      <c r="E91" s="6" t="str">
         <f aca="false">IF(Sheet1!E91="","",Sheet1!E91)</f>
         <v/>
       </c>
-      <c r="F91" s="5" t="str">
+      <c r="F91" s="6" t="str">
         <f aca="false">IF(Sheet1!F91="","",Sheet1!F91)</f>
         <v/>
       </c>
@@ -4240,30 +4244,30 @@
         <f aca="false">LEFT(F91,1)</f>
         <v/>
       </c>
-      <c r="I91" s="12"/>
-    </row>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="13"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="str">
         <f aca="false">IF(Sheet1!A92="","",Sheet1!A92)</f>
         <v/>
       </c>
-      <c r="B92" s="5" t="str">
+      <c r="B92" s="6" t="str">
         <f aca="false">IF(Sheet1!B92="","",Sheet1!B92)</f>
         <v/>
       </c>
-      <c r="C92" s="5" t="str">
+      <c r="C92" s="6" t="str">
         <f aca="false">IF(Sheet1!C92="","",Sheet1!C92)</f>
         <v/>
       </c>
-      <c r="D92" s="5" t="str">
+      <c r="D92" s="6" t="str">
         <f aca="false">IF(Sheet1!D92="","",Sheet1!D92)</f>
         <v/>
       </c>
-      <c r="E92" s="5" t="str">
+      <c r="E92" s="6" t="str">
         <f aca="false">IF(Sheet1!E92="","",Sheet1!E92)</f>
         <v/>
       </c>
-      <c r="F92" s="5" t="str">
+      <c r="F92" s="6" t="str">
         <f aca="false">IF(Sheet1!F92="","",Sheet1!F92)</f>
         <v/>
       </c>
@@ -4271,30 +4275,30 @@
         <f aca="false">LEFT(F92,1)</f>
         <v/>
       </c>
-      <c r="I92" s="12"/>
-    </row>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I92" s="13"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="str">
         <f aca="false">IF(Sheet1!A93="","",Sheet1!A93)</f>
         <v/>
       </c>
-      <c r="B93" s="5" t="str">
+      <c r="B93" s="6" t="str">
         <f aca="false">IF(Sheet1!B93="","",Sheet1!B93)</f>
         <v/>
       </c>
-      <c r="C93" s="5" t="str">
+      <c r="C93" s="6" t="str">
         <f aca="false">IF(Sheet1!C93="","",Sheet1!C93)</f>
         <v/>
       </c>
-      <c r="D93" s="5" t="str">
+      <c r="D93" s="6" t="str">
         <f aca="false">IF(Sheet1!D93="","",Sheet1!D93)</f>
         <v/>
       </c>
-      <c r="E93" s="5" t="str">
+      <c r="E93" s="6" t="str">
         <f aca="false">IF(Sheet1!E93="","",Sheet1!E93)</f>
         <v/>
       </c>
-      <c r="F93" s="5" t="str">
+      <c r="F93" s="6" t="str">
         <f aca="false">IF(Sheet1!F93="","",Sheet1!F93)</f>
         <v/>
       </c>
@@ -4302,30 +4306,30 @@
         <f aca="false">LEFT(F93,1)</f>
         <v/>
       </c>
-      <c r="I93" s="12"/>
-    </row>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I93" s="13"/>
+    </row>
+    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="str">
         <f aca="false">IF(Sheet1!A94="","",Sheet1!A94)</f>
         <v/>
       </c>
-      <c r="B94" s="5" t="str">
+      <c r="B94" s="6" t="str">
         <f aca="false">IF(Sheet1!B94="","",Sheet1!B94)</f>
         <v/>
       </c>
-      <c r="C94" s="5" t="str">
+      <c r="C94" s="6" t="str">
         <f aca="false">IF(Sheet1!C94="","",Sheet1!C94)</f>
         <v/>
       </c>
-      <c r="D94" s="5" t="str">
+      <c r="D94" s="6" t="str">
         <f aca="false">IF(Sheet1!D94="","",Sheet1!D94)</f>
         <v/>
       </c>
-      <c r="E94" s="5" t="str">
+      <c r="E94" s="6" t="str">
         <f aca="false">IF(Sheet1!E94="","",Sheet1!E94)</f>
         <v/>
       </c>
-      <c r="F94" s="5" t="str">
+      <c r="F94" s="6" t="str">
         <f aca="false">IF(Sheet1!F94="","",Sheet1!F94)</f>
         <v/>
       </c>
@@ -4333,30 +4337,30 @@
         <f aca="false">LEFT(F94,1)</f>
         <v/>
       </c>
-      <c r="I94" s="12"/>
-    </row>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I94" s="13"/>
+    </row>
+    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="str">
         <f aca="false">IF(Sheet1!A95="","",Sheet1!A95)</f>
         <v/>
       </c>
-      <c r="B95" s="5" t="str">
+      <c r="B95" s="6" t="str">
         <f aca="false">IF(Sheet1!B95="","",Sheet1!B95)</f>
         <v/>
       </c>
-      <c r="C95" s="5" t="str">
+      <c r="C95" s="6" t="str">
         <f aca="false">IF(Sheet1!C95="","",Sheet1!C95)</f>
         <v/>
       </c>
-      <c r="D95" s="5" t="str">
+      <c r="D95" s="6" t="str">
         <f aca="false">IF(Sheet1!D95="","",Sheet1!D95)</f>
         <v/>
       </c>
-      <c r="E95" s="5" t="str">
+      <c r="E95" s="6" t="str">
         <f aca="false">IF(Sheet1!E95="","",Sheet1!E95)</f>
         <v/>
       </c>
-      <c r="F95" s="5" t="str">
+      <c r="F95" s="6" t="str">
         <f aca="false">IF(Sheet1!F95="","",Sheet1!F95)</f>
         <v/>
       </c>
@@ -4364,30 +4368,30 @@
         <f aca="false">LEFT(F95,1)</f>
         <v/>
       </c>
-      <c r="I95" s="12"/>
-    </row>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I95" s="13"/>
+    </row>
+    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="str">
         <f aca="false">IF(Sheet1!A96="","",Sheet1!A96)</f>
         <v/>
       </c>
-      <c r="B96" s="5" t="str">
+      <c r="B96" s="6" t="str">
         <f aca="false">IF(Sheet1!B96="","",Sheet1!B96)</f>
         <v/>
       </c>
-      <c r="C96" s="5" t="str">
+      <c r="C96" s="6" t="str">
         <f aca="false">IF(Sheet1!C96="","",Sheet1!C96)</f>
         <v/>
       </c>
-      <c r="D96" s="5" t="str">
+      <c r="D96" s="6" t="str">
         <f aca="false">IF(Sheet1!D96="","",Sheet1!D96)</f>
         <v/>
       </c>
-      <c r="E96" s="5" t="str">
+      <c r="E96" s="6" t="str">
         <f aca="false">IF(Sheet1!E96="","",Sheet1!E96)</f>
         <v/>
       </c>
-      <c r="F96" s="5" t="str">
+      <c r="F96" s="6" t="str">
         <f aca="false">IF(Sheet1!F96="","",Sheet1!F96)</f>
         <v/>
       </c>
@@ -4395,30 +4399,30 @@
         <f aca="false">LEFT(F96,1)</f>
         <v/>
       </c>
-      <c r="I96" s="12"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I96" s="13"/>
+    </row>
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="str">
         <f aca="false">IF(Sheet1!A97="","",Sheet1!A97)</f>
         <v/>
       </c>
-      <c r="B97" s="5" t="str">
+      <c r="B97" s="6" t="str">
         <f aca="false">IF(Sheet1!B97="","",Sheet1!B97)</f>
         <v/>
       </c>
-      <c r="C97" s="5" t="str">
+      <c r="C97" s="6" t="str">
         <f aca="false">IF(Sheet1!C97="","",Sheet1!C97)</f>
         <v/>
       </c>
-      <c r="D97" s="5" t="str">
+      <c r="D97" s="6" t="str">
         <f aca="false">IF(Sheet1!D97="","",Sheet1!D97)</f>
         <v/>
       </c>
-      <c r="E97" s="5" t="str">
+      <c r="E97" s="6" t="str">
         <f aca="false">IF(Sheet1!E97="","",Sheet1!E97)</f>
         <v/>
       </c>
-      <c r="F97" s="5" t="str">
+      <c r="F97" s="6" t="str">
         <f aca="false">IF(Sheet1!F97="","",Sheet1!F97)</f>
         <v/>
       </c>
@@ -4426,30 +4430,30 @@
         <f aca="false">LEFT(F97,1)</f>
         <v/>
       </c>
-      <c r="I97" s="12"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I97" s="13"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="str">
         <f aca="false">IF(Sheet1!A98="","",Sheet1!A98)</f>
         <v/>
       </c>
-      <c r="B98" s="5" t="str">
+      <c r="B98" s="6" t="str">
         <f aca="false">IF(Sheet1!B98="","",Sheet1!B98)</f>
         <v/>
       </c>
-      <c r="C98" s="5" t="str">
+      <c r="C98" s="6" t="str">
         <f aca="false">IF(Sheet1!C98="","",Sheet1!C98)</f>
         <v/>
       </c>
-      <c r="D98" s="5" t="str">
+      <c r="D98" s="6" t="str">
         <f aca="false">IF(Sheet1!D98="","",Sheet1!D98)</f>
         <v/>
       </c>
-      <c r="E98" s="5" t="str">
+      <c r="E98" s="6" t="str">
         <f aca="false">IF(Sheet1!E98="","",Sheet1!E98)</f>
         <v/>
       </c>
-      <c r="F98" s="5" t="str">
+      <c r="F98" s="6" t="str">
         <f aca="false">IF(Sheet1!F98="","",Sheet1!F98)</f>
         <v/>
       </c>
@@ -4457,30 +4461,30 @@
         <f aca="false">LEFT(F98,1)</f>
         <v/>
       </c>
-      <c r="I98" s="12"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I98" s="13"/>
+    </row>
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="str">
         <f aca="false">IF(Sheet1!A99="","",Sheet1!A99)</f>
         <v/>
       </c>
-      <c r="B99" s="5" t="str">
+      <c r="B99" s="6" t="str">
         <f aca="false">IF(Sheet1!B99="","",Sheet1!B99)</f>
         <v/>
       </c>
-      <c r="C99" s="5" t="str">
+      <c r="C99" s="6" t="str">
         <f aca="false">IF(Sheet1!C99="","",Sheet1!C99)</f>
         <v/>
       </c>
-      <c r="D99" s="5" t="str">
+      <c r="D99" s="6" t="str">
         <f aca="false">IF(Sheet1!D99="","",Sheet1!D99)</f>
         <v/>
       </c>
-      <c r="E99" s="5" t="str">
+      <c r="E99" s="6" t="str">
         <f aca="false">IF(Sheet1!E99="","",Sheet1!E99)</f>
         <v/>
       </c>
-      <c r="F99" s="5" t="str">
+      <c r="F99" s="6" t="str">
         <f aca="false">IF(Sheet1!F99="","",Sheet1!F99)</f>
         <v/>
       </c>
@@ -4488,30 +4492,30 @@
         <f aca="false">LEFT(F99,1)</f>
         <v/>
       </c>
-      <c r="I99" s="12"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I99" s="13"/>
+    </row>
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="str">
         <f aca="false">IF(Sheet1!A100="","",Sheet1!A100)</f>
         <v/>
       </c>
-      <c r="B100" s="5" t="str">
+      <c r="B100" s="6" t="str">
         <f aca="false">IF(Sheet1!B100="","",Sheet1!B100)</f>
         <v/>
       </c>
-      <c r="C100" s="5" t="str">
+      <c r="C100" s="6" t="str">
         <f aca="false">IF(Sheet1!C100="","",Sheet1!C100)</f>
         <v/>
       </c>
-      <c r="D100" s="5" t="str">
+      <c r="D100" s="6" t="str">
         <f aca="false">IF(Sheet1!D100="","",Sheet1!D100)</f>
         <v/>
       </c>
-      <c r="E100" s="5" t="str">
+      <c r="E100" s="6" t="str">
         <f aca="false">IF(Sheet1!E100="","",Sheet1!E100)</f>
         <v/>
       </c>
-      <c r="F100" s="5" t="str">
+      <c r="F100" s="6" t="str">
         <f aca="false">IF(Sheet1!F100="","",Sheet1!F100)</f>
         <v/>
       </c>
@@ -4519,30 +4523,30 @@
         <f aca="false">LEFT(F100,1)</f>
         <v/>
       </c>
-      <c r="I100" s="12"/>
-    </row>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I100" s="13"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="str">
         <f aca="false">IF(Sheet1!A101="","",Sheet1!A101)</f>
         <v/>
       </c>
-      <c r="B101" s="5" t="str">
+      <c r="B101" s="6" t="str">
         <f aca="false">IF(Sheet1!B101="","",Sheet1!B101)</f>
         <v/>
       </c>
-      <c r="C101" s="5" t="str">
+      <c r="C101" s="6" t="str">
         <f aca="false">IF(Sheet1!C101="","",Sheet1!C101)</f>
         <v/>
       </c>
-      <c r="D101" s="5" t="str">
+      <c r="D101" s="6" t="str">
         <f aca="false">IF(Sheet1!D101="","",Sheet1!D101)</f>
         <v/>
       </c>
-      <c r="E101" s="5" t="str">
+      <c r="E101" s="6" t="str">
         <f aca="false">IF(Sheet1!E101="","",Sheet1!E101)</f>
         <v/>
       </c>
-      <c r="F101" s="5" t="str">
+      <c r="F101" s="6" t="str">
         <f aca="false">IF(Sheet1!F101="","",Sheet1!F101)</f>
         <v/>
       </c>
@@ -4550,30 +4554,30 @@
         <f aca="false">LEFT(F101,1)</f>
         <v/>
       </c>
-      <c r="I101" s="12"/>
-    </row>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I101" s="13"/>
+    </row>
+    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="str">
         <f aca="false">IF(Sheet1!A102="","",Sheet1!A102)</f>
         <v/>
       </c>
-      <c r="B102" s="5" t="str">
+      <c r="B102" s="6" t="str">
         <f aca="false">IF(Sheet1!B102="","",Sheet1!B102)</f>
         <v/>
       </c>
-      <c r="C102" s="5" t="str">
+      <c r="C102" s="6" t="str">
         <f aca="false">IF(Sheet1!C102="","",Sheet1!C102)</f>
         <v/>
       </c>
-      <c r="D102" s="5" t="str">
+      <c r="D102" s="6" t="str">
         <f aca="false">IF(Sheet1!D102="","",Sheet1!D102)</f>
         <v/>
       </c>
-      <c r="E102" s="5" t="str">
+      <c r="E102" s="6" t="str">
         <f aca="false">IF(Sheet1!E102="","",Sheet1!E102)</f>
         <v/>
       </c>
-      <c r="F102" s="5" t="str">
+      <c r="F102" s="6" t="str">
         <f aca="false">IF(Sheet1!F102="","",Sheet1!F102)</f>
         <v/>
       </c>
@@ -4581,30 +4585,30 @@
         <f aca="false">LEFT(F102,1)</f>
         <v/>
       </c>
-      <c r="I102" s="12"/>
-    </row>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I102" s="13"/>
+    </row>
+    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="str">
         <f aca="false">IF(Sheet1!A103="","",Sheet1!A103)</f>
         <v/>
       </c>
-      <c r="B103" s="5" t="str">
+      <c r="B103" s="6" t="str">
         <f aca="false">IF(Sheet1!B103="","",Sheet1!B103)</f>
         <v/>
       </c>
-      <c r="C103" s="5" t="str">
+      <c r="C103" s="6" t="str">
         <f aca="false">IF(Sheet1!C103="","",Sheet1!C103)</f>
         <v/>
       </c>
-      <c r="D103" s="5" t="str">
+      <c r="D103" s="6" t="str">
         <f aca="false">IF(Sheet1!D103="","",Sheet1!D103)</f>
         <v/>
       </c>
-      <c r="E103" s="5" t="str">
+      <c r="E103" s="6" t="str">
         <f aca="false">IF(Sheet1!E103="","",Sheet1!E103)</f>
         <v/>
       </c>
-      <c r="F103" s="5" t="str">
+      <c r="F103" s="6" t="str">
         <f aca="false">IF(Sheet1!F103="","",Sheet1!F103)</f>
         <v/>
       </c>
@@ -4612,30 +4616,30 @@
         <f aca="false">LEFT(F103,1)</f>
         <v/>
       </c>
-      <c r="I103" s="12"/>
-    </row>
-    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I103" s="13"/>
+    </row>
+    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="str">
         <f aca="false">IF(Sheet1!A104="","",Sheet1!A104)</f>
         <v/>
       </c>
-      <c r="B104" s="5" t="str">
+      <c r="B104" s="6" t="str">
         <f aca="false">IF(Sheet1!B104="","",Sheet1!B104)</f>
         <v/>
       </c>
-      <c r="C104" s="5" t="str">
+      <c r="C104" s="6" t="str">
         <f aca="false">IF(Sheet1!C104="","",Sheet1!C104)</f>
         <v/>
       </c>
-      <c r="D104" s="5" t="str">
+      <c r="D104" s="6" t="str">
         <f aca="false">IF(Sheet1!D104="","",Sheet1!D104)</f>
         <v/>
       </c>
-      <c r="E104" s="5" t="str">
+      <c r="E104" s="6" t="str">
         <f aca="false">IF(Sheet1!E104="","",Sheet1!E104)</f>
         <v/>
       </c>
-      <c r="F104" s="5" t="str">
+      <c r="F104" s="6" t="str">
         <f aca="false">IF(Sheet1!F104="","",Sheet1!F104)</f>
         <v/>
       </c>
@@ -4643,30 +4647,30 @@
         <f aca="false">LEFT(F104,1)</f>
         <v/>
       </c>
-      <c r="I104" s="12"/>
-    </row>
-    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I104" s="13"/>
+    </row>
+    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="str">
         <f aca="false">IF(Sheet1!A105="","",Sheet1!A105)</f>
         <v/>
       </c>
-      <c r="B105" s="5" t="str">
+      <c r="B105" s="6" t="str">
         <f aca="false">IF(Sheet1!B105="","",Sheet1!B105)</f>
         <v/>
       </c>
-      <c r="C105" s="5" t="str">
+      <c r="C105" s="6" t="str">
         <f aca="false">IF(Sheet1!C105="","",Sheet1!C105)</f>
         <v/>
       </c>
-      <c r="D105" s="5" t="str">
+      <c r="D105" s="6" t="str">
         <f aca="false">IF(Sheet1!D105="","",Sheet1!D105)</f>
         <v/>
       </c>
-      <c r="E105" s="5" t="str">
+      <c r="E105" s="6" t="str">
         <f aca="false">IF(Sheet1!E105="","",Sheet1!E105)</f>
         <v/>
       </c>
-      <c r="F105" s="5" t="str">
+      <c r="F105" s="6" t="str">
         <f aca="false">IF(Sheet1!F105="","",Sheet1!F105)</f>
         <v/>
       </c>
@@ -4674,30 +4678,30 @@
         <f aca="false">LEFT(F105,1)</f>
         <v/>
       </c>
-      <c r="I105" s="12"/>
-    </row>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I105" s="13"/>
+    </row>
+    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="str">
         <f aca="false">IF(Sheet1!A106="","",Sheet1!A106)</f>
         <v/>
       </c>
-      <c r="B106" s="5" t="str">
+      <c r="B106" s="6" t="str">
         <f aca="false">IF(Sheet1!B106="","",Sheet1!B106)</f>
         <v/>
       </c>
-      <c r="C106" s="5" t="str">
+      <c r="C106" s="6" t="str">
         <f aca="false">IF(Sheet1!C106="","",Sheet1!C106)</f>
         <v/>
       </c>
-      <c r="D106" s="5" t="str">
+      <c r="D106" s="6" t="str">
         <f aca="false">IF(Sheet1!D106="","",Sheet1!D106)</f>
         <v/>
       </c>
-      <c r="E106" s="5" t="str">
+      <c r="E106" s="6" t="str">
         <f aca="false">IF(Sheet1!E106="","",Sheet1!E106)</f>
         <v/>
       </c>
-      <c r="F106" s="5" t="str">
+      <c r="F106" s="6" t="str">
         <f aca="false">IF(Sheet1!F106="","",Sheet1!F106)</f>
         <v/>
       </c>
@@ -4705,30 +4709,30 @@
         <f aca="false">LEFT(F106,1)</f>
         <v/>
       </c>
-      <c r="I106" s="12"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I106" s="13"/>
+    </row>
+    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="str">
         <f aca="false">IF(Sheet1!A107="","",Sheet1!A107)</f>
         <v/>
       </c>
-      <c r="B107" s="5" t="str">
+      <c r="B107" s="6" t="str">
         <f aca="false">IF(Sheet1!B107="","",Sheet1!B107)</f>
         <v/>
       </c>
-      <c r="C107" s="5" t="str">
+      <c r="C107" s="6" t="str">
         <f aca="false">IF(Sheet1!C107="","",Sheet1!C107)</f>
         <v/>
       </c>
-      <c r="D107" s="5" t="str">
+      <c r="D107" s="6" t="str">
         <f aca="false">IF(Sheet1!D107="","",Sheet1!D107)</f>
         <v/>
       </c>
-      <c r="E107" s="5" t="str">
+      <c r="E107" s="6" t="str">
         <f aca="false">IF(Sheet1!E107="","",Sheet1!E107)</f>
         <v/>
       </c>
-      <c r="F107" s="5" t="str">
+      <c r="F107" s="6" t="str">
         <f aca="false">IF(Sheet1!F107="","",Sheet1!F107)</f>
         <v/>
       </c>
@@ -4736,30 +4740,30 @@
         <f aca="false">LEFT(F107,1)</f>
         <v/>
       </c>
-      <c r="I107" s="12"/>
-    </row>
-    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I107" s="13"/>
+    </row>
+    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="str">
         <f aca="false">IF(Sheet1!A108="","",Sheet1!A108)</f>
         <v/>
       </c>
-      <c r="B108" s="5" t="str">
+      <c r="B108" s="6" t="str">
         <f aca="false">IF(Sheet1!B108="","",Sheet1!B108)</f>
         <v/>
       </c>
-      <c r="C108" s="5" t="str">
+      <c r="C108" s="6" t="str">
         <f aca="false">IF(Sheet1!C108="","",Sheet1!C108)</f>
         <v/>
       </c>
-      <c r="D108" s="5" t="str">
+      <c r="D108" s="6" t="str">
         <f aca="false">IF(Sheet1!D108="","",Sheet1!D108)</f>
         <v/>
       </c>
-      <c r="E108" s="5" t="str">
+      <c r="E108" s="6" t="str">
         <f aca="false">IF(Sheet1!E108="","",Sheet1!E108)</f>
         <v/>
       </c>
-      <c r="F108" s="5" t="str">
+      <c r="F108" s="6" t="str">
         <f aca="false">IF(Sheet1!F108="","",Sheet1!F108)</f>
         <v/>
       </c>
@@ -4767,30 +4771,30 @@
         <f aca="false">LEFT(F108,1)</f>
         <v/>
       </c>
-      <c r="I108" s="12"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I108" s="13"/>
+    </row>
+    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="str">
         <f aca="false">IF(Sheet1!A109="","",Sheet1!A109)</f>
         <v/>
       </c>
-      <c r="B109" s="5" t="str">
+      <c r="B109" s="6" t="str">
         <f aca="false">IF(Sheet1!B109="","",Sheet1!B109)</f>
         <v/>
       </c>
-      <c r="C109" s="5" t="str">
+      <c r="C109" s="6" t="str">
         <f aca="false">IF(Sheet1!C109="","",Sheet1!C109)</f>
         <v/>
       </c>
-      <c r="D109" s="5" t="str">
+      <c r="D109" s="6" t="str">
         <f aca="false">IF(Sheet1!D109="","",Sheet1!D109)</f>
         <v/>
       </c>
-      <c r="E109" s="5" t="str">
+      <c r="E109" s="6" t="str">
         <f aca="false">IF(Sheet1!E109="","",Sheet1!E109)</f>
         <v/>
       </c>
-      <c r="F109" s="5" t="str">
+      <c r="F109" s="6" t="str">
         <f aca="false">IF(Sheet1!F109="","",Sheet1!F109)</f>
         <v/>
       </c>
@@ -4798,30 +4802,30 @@
         <f aca="false">LEFT(F109,1)</f>
         <v/>
       </c>
-      <c r="I109" s="12"/>
-    </row>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I109" s="13"/>
+    </row>
+    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="str">
         <f aca="false">IF(Sheet1!A110="","",Sheet1!A110)</f>
         <v/>
       </c>
-      <c r="B110" s="5" t="str">
+      <c r="B110" s="6" t="str">
         <f aca="false">IF(Sheet1!B110="","",Sheet1!B110)</f>
         <v/>
       </c>
-      <c r="C110" s="5" t="str">
+      <c r="C110" s="6" t="str">
         <f aca="false">IF(Sheet1!C110="","",Sheet1!C110)</f>
         <v/>
       </c>
-      <c r="D110" s="5" t="str">
+      <c r="D110" s="6" t="str">
         <f aca="false">IF(Sheet1!D110="","",Sheet1!D110)</f>
         <v/>
       </c>
-      <c r="E110" s="5" t="str">
+      <c r="E110" s="6" t="str">
         <f aca="false">IF(Sheet1!E110="","",Sheet1!E110)</f>
         <v/>
       </c>
-      <c r="F110" s="5" t="str">
+      <c r="F110" s="6" t="str">
         <f aca="false">IF(Sheet1!F110="","",Sheet1!F110)</f>
         <v/>
       </c>
@@ -4829,30 +4833,30 @@
         <f aca="false">LEFT(F110,1)</f>
         <v/>
       </c>
-      <c r="I110" s="12"/>
-    </row>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I110" s="13"/>
+    </row>
+    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="str">
         <f aca="false">IF(Sheet1!A111="","",Sheet1!A111)</f>
         <v/>
       </c>
-      <c r="B111" s="5" t="str">
+      <c r="B111" s="6" t="str">
         <f aca="false">IF(Sheet1!B111="","",Sheet1!B111)</f>
         <v/>
       </c>
-      <c r="C111" s="5" t="str">
+      <c r="C111" s="6" t="str">
         <f aca="false">IF(Sheet1!C111="","",Sheet1!C111)</f>
         <v/>
       </c>
-      <c r="D111" s="5" t="str">
+      <c r="D111" s="6" t="str">
         <f aca="false">IF(Sheet1!D111="","",Sheet1!D111)</f>
         <v/>
       </c>
-      <c r="E111" s="5" t="str">
+      <c r="E111" s="6" t="str">
         <f aca="false">IF(Sheet1!E111="","",Sheet1!E111)</f>
         <v/>
       </c>
-      <c r="F111" s="5" t="str">
+      <c r="F111" s="6" t="str">
         <f aca="false">IF(Sheet1!F111="","",Sheet1!F111)</f>
         <v/>
       </c>
@@ -4860,30 +4864,30 @@
         <f aca="false">LEFT(F111,1)</f>
         <v/>
       </c>
-      <c r="I111" s="12"/>
-    </row>
-    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I111" s="13"/>
+    </row>
+    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="str">
         <f aca="false">IF(Sheet1!A112="","",Sheet1!A112)</f>
         <v/>
       </c>
-      <c r="B112" s="5" t="str">
+      <c r="B112" s="6" t="str">
         <f aca="false">IF(Sheet1!B112="","",Sheet1!B112)</f>
         <v/>
       </c>
-      <c r="C112" s="5" t="str">
+      <c r="C112" s="6" t="str">
         <f aca="false">IF(Sheet1!C112="","",Sheet1!C112)</f>
         <v/>
       </c>
-      <c r="D112" s="5" t="str">
+      <c r="D112" s="6" t="str">
         <f aca="false">IF(Sheet1!D112="","",Sheet1!D112)</f>
         <v/>
       </c>
-      <c r="E112" s="5" t="str">
+      <c r="E112" s="6" t="str">
         <f aca="false">IF(Sheet1!E112="","",Sheet1!E112)</f>
         <v/>
       </c>
-      <c r="F112" s="5" t="str">
+      <c r="F112" s="6" t="str">
         <f aca="false">IF(Sheet1!F112="","",Sheet1!F112)</f>
         <v/>
       </c>
@@ -4891,30 +4895,30 @@
         <f aca="false">LEFT(F112,1)</f>
         <v/>
       </c>
-      <c r="I112" s="12"/>
-    </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I112" s="13"/>
+    </row>
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="str">
         <f aca="false">IF(Sheet1!A113="","",Sheet1!A113)</f>
         <v/>
       </c>
-      <c r="B113" s="5" t="str">
+      <c r="B113" s="6" t="str">
         <f aca="false">IF(Sheet1!B113="","",Sheet1!B113)</f>
         <v/>
       </c>
-      <c r="C113" s="5" t="str">
+      <c r="C113" s="6" t="str">
         <f aca="false">IF(Sheet1!C113="","",Sheet1!C113)</f>
         <v/>
       </c>
-      <c r="D113" s="5" t="str">
+      <c r="D113" s="6" t="str">
         <f aca="false">IF(Sheet1!D113="","",Sheet1!D113)</f>
         <v/>
       </c>
-      <c r="E113" s="5" t="str">
+      <c r="E113" s="6" t="str">
         <f aca="false">IF(Sheet1!E113="","",Sheet1!E113)</f>
         <v/>
       </c>
-      <c r="F113" s="5" t="str">
+      <c r="F113" s="6" t="str">
         <f aca="false">IF(Sheet1!F113="","",Sheet1!F113)</f>
         <v/>
       </c>
@@ -4922,30 +4926,30 @@
         <f aca="false">LEFT(F113,1)</f>
         <v/>
       </c>
-      <c r="I113" s="12"/>
-    </row>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I113" s="13"/>
+    </row>
+    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="str">
         <f aca="false">IF(Sheet1!A114="","",Sheet1!A114)</f>
         <v/>
       </c>
-      <c r="B114" s="5" t="str">
+      <c r="B114" s="6" t="str">
         <f aca="false">IF(Sheet1!B114="","",Sheet1!B114)</f>
         <v/>
       </c>
-      <c r="C114" s="5" t="str">
+      <c r="C114" s="6" t="str">
         <f aca="false">IF(Sheet1!C114="","",Sheet1!C114)</f>
         <v/>
       </c>
-      <c r="D114" s="5" t="str">
+      <c r="D114" s="6" t="str">
         <f aca="false">IF(Sheet1!D114="","",Sheet1!D114)</f>
         <v/>
       </c>
-      <c r="E114" s="5" t="str">
+      <c r="E114" s="6" t="str">
         <f aca="false">IF(Sheet1!E114="","",Sheet1!E114)</f>
         <v/>
       </c>
-      <c r="F114" s="5" t="str">
+      <c r="F114" s="6" t="str">
         <f aca="false">IF(Sheet1!F114="","",Sheet1!F114)</f>
         <v/>
       </c>
@@ -4953,30 +4957,30 @@
         <f aca="false">LEFT(F114,1)</f>
         <v/>
       </c>
-      <c r="I114" s="12"/>
-    </row>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I114" s="13"/>
+    </row>
+    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="str">
         <f aca="false">IF(Sheet1!A115="","",Sheet1!A115)</f>
         <v/>
       </c>
-      <c r="B115" s="5" t="str">
+      <c r="B115" s="6" t="str">
         <f aca="false">IF(Sheet1!B115="","",Sheet1!B115)</f>
         <v/>
       </c>
-      <c r="C115" s="5" t="str">
+      <c r="C115" s="6" t="str">
         <f aca="false">IF(Sheet1!C115="","",Sheet1!C115)</f>
         <v/>
       </c>
-      <c r="D115" s="5" t="str">
+      <c r="D115" s="6" t="str">
         <f aca="false">IF(Sheet1!D115="","",Sheet1!D115)</f>
         <v/>
       </c>
-      <c r="E115" s="5" t="str">
+      <c r="E115" s="6" t="str">
         <f aca="false">IF(Sheet1!E115="","",Sheet1!E115)</f>
         <v/>
       </c>
-      <c r="F115" s="5" t="str">
+      <c r="F115" s="6" t="str">
         <f aca="false">IF(Sheet1!F115="","",Sheet1!F115)</f>
         <v/>
       </c>
@@ -4984,30 +4988,30 @@
         <f aca="false">LEFT(F115,1)</f>
         <v/>
       </c>
-      <c r="I115" s="12"/>
-    </row>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I115" s="13"/>
+    </row>
+    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="str">
         <f aca="false">IF(Sheet1!A116="","",Sheet1!A116)</f>
         <v/>
       </c>
-      <c r="B116" s="5" t="str">
+      <c r="B116" s="6" t="str">
         <f aca="false">IF(Sheet1!B116="","",Sheet1!B116)</f>
         <v/>
       </c>
-      <c r="C116" s="5" t="str">
+      <c r="C116" s="6" t="str">
         <f aca="false">IF(Sheet1!C116="","",Sheet1!C116)</f>
         <v/>
       </c>
-      <c r="D116" s="5" t="str">
+      <c r="D116" s="6" t="str">
         <f aca="false">IF(Sheet1!D116="","",Sheet1!D116)</f>
         <v/>
       </c>
-      <c r="E116" s="5" t="str">
+      <c r="E116" s="6" t="str">
         <f aca="false">IF(Sheet1!E116="","",Sheet1!E116)</f>
         <v/>
       </c>
-      <c r="F116" s="5" t="str">
+      <c r="F116" s="6" t="str">
         <f aca="false">IF(Sheet1!F116="","",Sheet1!F116)</f>
         <v/>
       </c>
@@ -5015,30 +5019,30 @@
         <f aca="false">LEFT(F116,1)</f>
         <v/>
       </c>
-      <c r="I116" s="12"/>
-    </row>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I116" s="13"/>
+    </row>
+    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="str">
         <f aca="false">IF(Sheet1!A117="","",Sheet1!A117)</f>
         <v/>
       </c>
-      <c r="B117" s="5" t="str">
+      <c r="B117" s="6" t="str">
         <f aca="false">IF(Sheet1!B117="","",Sheet1!B117)</f>
         <v/>
       </c>
-      <c r="C117" s="5" t="str">
+      <c r="C117" s="6" t="str">
         <f aca="false">IF(Sheet1!C117="","",Sheet1!C117)</f>
         <v/>
       </c>
-      <c r="D117" s="5" t="str">
+      <c r="D117" s="6" t="str">
         <f aca="false">IF(Sheet1!D117="","",Sheet1!D117)</f>
         <v/>
       </c>
-      <c r="E117" s="5" t="str">
+      <c r="E117" s="6" t="str">
         <f aca="false">IF(Sheet1!E117="","",Sheet1!E117)</f>
         <v/>
       </c>
-      <c r="F117" s="5" t="str">
+      <c r="F117" s="6" t="str">
         <f aca="false">IF(Sheet1!F117="","",Sheet1!F117)</f>
         <v/>
       </c>
@@ -5046,30 +5050,30 @@
         <f aca="false">LEFT(F117,1)</f>
         <v/>
       </c>
-      <c r="I117" s="12"/>
-    </row>
-    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I117" s="13"/>
+    </row>
+    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="str">
         <f aca="false">IF(Sheet1!A118="","",Sheet1!A118)</f>
         <v/>
       </c>
-      <c r="B118" s="5" t="str">
+      <c r="B118" s="6" t="str">
         <f aca="false">IF(Sheet1!B118="","",Sheet1!B118)</f>
         <v/>
       </c>
-      <c r="C118" s="5" t="str">
+      <c r="C118" s="6" t="str">
         <f aca="false">IF(Sheet1!C118="","",Sheet1!C118)</f>
         <v/>
       </c>
-      <c r="D118" s="5" t="str">
+      <c r="D118" s="6" t="str">
         <f aca="false">IF(Sheet1!D118="","",Sheet1!D118)</f>
         <v/>
       </c>
-      <c r="E118" s="5" t="str">
+      <c r="E118" s="6" t="str">
         <f aca="false">IF(Sheet1!E118="","",Sheet1!E118)</f>
         <v/>
       </c>
-      <c r="F118" s="5" t="str">
+      <c r="F118" s="6" t="str">
         <f aca="false">IF(Sheet1!F118="","",Sheet1!F118)</f>
         <v/>
       </c>
@@ -5077,30 +5081,30 @@
         <f aca="false">LEFT(F118,1)</f>
         <v/>
       </c>
-      <c r="I118" s="12"/>
-    </row>
-    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I118" s="13"/>
+    </row>
+    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="str">
         <f aca="false">IF(Sheet1!A119="","",Sheet1!A119)</f>
         <v/>
       </c>
-      <c r="B119" s="5" t="str">
+      <c r="B119" s="6" t="str">
         <f aca="false">IF(Sheet1!B119="","",Sheet1!B119)</f>
         <v/>
       </c>
-      <c r="C119" s="5" t="str">
+      <c r="C119" s="6" t="str">
         <f aca="false">IF(Sheet1!C119="","",Sheet1!C119)</f>
         <v/>
       </c>
-      <c r="D119" s="5" t="str">
+      <c r="D119" s="6" t="str">
         <f aca="false">IF(Sheet1!D119="","",Sheet1!D119)</f>
         <v/>
       </c>
-      <c r="E119" s="5" t="str">
+      <c r="E119" s="6" t="str">
         <f aca="false">IF(Sheet1!E119="","",Sheet1!E119)</f>
         <v/>
       </c>
-      <c r="F119" s="5" t="str">
+      <c r="F119" s="6" t="str">
         <f aca="false">IF(Sheet1!F119="","",Sheet1!F119)</f>
         <v/>
       </c>
@@ -5108,30 +5112,30 @@
         <f aca="false">LEFT(F119,1)</f>
         <v/>
       </c>
-      <c r="I119" s="12"/>
-    </row>
-    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I119" s="13"/>
+    </row>
+    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="str">
         <f aca="false">IF(Sheet1!A120="","",Sheet1!A120)</f>
         <v/>
       </c>
-      <c r="B120" s="5" t="str">
+      <c r="B120" s="6" t="str">
         <f aca="false">IF(Sheet1!B120="","",Sheet1!B120)</f>
         <v/>
       </c>
-      <c r="C120" s="5" t="str">
+      <c r="C120" s="6" t="str">
         <f aca="false">IF(Sheet1!C120="","",Sheet1!C120)</f>
         <v/>
       </c>
-      <c r="D120" s="5" t="str">
+      <c r="D120" s="6" t="str">
         <f aca="false">IF(Sheet1!D120="","",Sheet1!D120)</f>
         <v/>
       </c>
-      <c r="E120" s="5" t="str">
+      <c r="E120" s="6" t="str">
         <f aca="false">IF(Sheet1!E120="","",Sheet1!E120)</f>
         <v/>
       </c>
-      <c r="F120" s="5" t="str">
+      <c r="F120" s="6" t="str">
         <f aca="false">IF(Sheet1!F120="","",Sheet1!F120)</f>
         <v/>
       </c>
@@ -5139,30 +5143,30 @@
         <f aca="false">LEFT(F120,1)</f>
         <v/>
       </c>
-      <c r="I120" s="12"/>
-    </row>
-    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I120" s="13"/>
+    </row>
+    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="str">
         <f aca="false">IF(Sheet1!A121="","",Sheet1!A121)</f>
         <v/>
       </c>
-      <c r="B121" s="5" t="str">
+      <c r="B121" s="6" t="str">
         <f aca="false">IF(Sheet1!B121="","",Sheet1!B121)</f>
         <v/>
       </c>
-      <c r="C121" s="5" t="str">
+      <c r="C121" s="6" t="str">
         <f aca="false">IF(Sheet1!C121="","",Sheet1!C121)</f>
         <v/>
       </c>
-      <c r="D121" s="5" t="str">
+      <c r="D121" s="6" t="str">
         <f aca="false">IF(Sheet1!D121="","",Sheet1!D121)</f>
         <v/>
       </c>
-      <c r="E121" s="5" t="str">
+      <c r="E121" s="6" t="str">
         <f aca="false">IF(Sheet1!E121="","",Sheet1!E121)</f>
         <v/>
       </c>
-      <c r="F121" s="5" t="str">
+      <c r="F121" s="6" t="str">
         <f aca="false">IF(Sheet1!F121="","",Sheet1!F121)</f>
         <v/>
       </c>
@@ -5170,30 +5174,30 @@
         <f aca="false">LEFT(F121,1)</f>
         <v/>
       </c>
-      <c r="I121" s="12"/>
-    </row>
-    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I121" s="13"/>
+    </row>
+    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="str">
         <f aca="false">IF(Sheet1!A122="","",Sheet1!A122)</f>
         <v/>
       </c>
-      <c r="B122" s="5" t="str">
+      <c r="B122" s="6" t="str">
         <f aca="false">IF(Sheet1!B122="","",Sheet1!B122)</f>
         <v/>
       </c>
-      <c r="C122" s="5" t="str">
+      <c r="C122" s="6" t="str">
         <f aca="false">IF(Sheet1!C122="","",Sheet1!C122)</f>
         <v/>
       </c>
-      <c r="D122" s="5" t="str">
+      <c r="D122" s="6" t="str">
         <f aca="false">IF(Sheet1!D122="","",Sheet1!D122)</f>
         <v/>
       </c>
-      <c r="E122" s="5" t="str">
+      <c r="E122" s="6" t="str">
         <f aca="false">IF(Sheet1!E122="","",Sheet1!E122)</f>
         <v/>
       </c>
-      <c r="F122" s="5" t="str">
+      <c r="F122" s="6" t="str">
         <f aca="false">IF(Sheet1!F122="","",Sheet1!F122)</f>
         <v/>
       </c>
@@ -5201,30 +5205,30 @@
         <f aca="false">LEFT(F122,1)</f>
         <v/>
       </c>
-      <c r="I122" s="12"/>
-    </row>
-    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I122" s="13"/>
+    </row>
+    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="str">
         <f aca="false">IF(Sheet1!A123="","",Sheet1!A123)</f>
         <v/>
       </c>
-      <c r="B123" s="5" t="str">
+      <c r="B123" s="6" t="str">
         <f aca="false">IF(Sheet1!B123="","",Sheet1!B123)</f>
         <v/>
       </c>
-      <c r="C123" s="5" t="str">
+      <c r="C123" s="6" t="str">
         <f aca="false">IF(Sheet1!C123="","",Sheet1!C123)</f>
         <v/>
       </c>
-      <c r="D123" s="5" t="str">
+      <c r="D123" s="6" t="str">
         <f aca="false">IF(Sheet1!D123="","",Sheet1!D123)</f>
         <v/>
       </c>
-      <c r="E123" s="5" t="str">
+      <c r="E123" s="6" t="str">
         <f aca="false">IF(Sheet1!E123="","",Sheet1!E123)</f>
         <v/>
       </c>
-      <c r="F123" s="5" t="str">
+      <c r="F123" s="6" t="str">
         <f aca="false">IF(Sheet1!F123="","",Sheet1!F123)</f>
         <v/>
       </c>
@@ -5232,30 +5236,30 @@
         <f aca="false">LEFT(F123,1)</f>
         <v/>
       </c>
-      <c r="I123" s="12"/>
-    </row>
-    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I123" s="13"/>
+    </row>
+    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="str">
         <f aca="false">IF(Sheet1!A124="","",Sheet1!A124)</f>
         <v/>
       </c>
-      <c r="B124" s="5" t="str">
+      <c r="B124" s="6" t="str">
         <f aca="false">IF(Sheet1!B124="","",Sheet1!B124)</f>
         <v/>
       </c>
-      <c r="C124" s="5" t="str">
+      <c r="C124" s="6" t="str">
         <f aca="false">IF(Sheet1!C124="","",Sheet1!C124)</f>
         <v/>
       </c>
-      <c r="D124" s="5" t="str">
+      <c r="D124" s="6" t="str">
         <f aca="false">IF(Sheet1!D124="","",Sheet1!D124)</f>
         <v/>
       </c>
-      <c r="E124" s="5" t="str">
+      <c r="E124" s="6" t="str">
         <f aca="false">IF(Sheet1!E124="","",Sheet1!E124)</f>
         <v/>
       </c>
-      <c r="F124" s="5" t="str">
+      <c r="F124" s="6" t="str">
         <f aca="false">IF(Sheet1!F124="","",Sheet1!F124)</f>
         <v/>
       </c>
@@ -5263,30 +5267,30 @@
         <f aca="false">LEFT(F124,1)</f>
         <v/>
       </c>
-      <c r="I124" s="12"/>
-    </row>
-    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="13"/>
+    </row>
+    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="str">
         <f aca="false">IF(Sheet1!A125="","",Sheet1!A125)</f>
         <v/>
       </c>
-      <c r="B125" s="5" t="str">
+      <c r="B125" s="6" t="str">
         <f aca="false">IF(Sheet1!B125="","",Sheet1!B125)</f>
         <v/>
       </c>
-      <c r="C125" s="5" t="str">
+      <c r="C125" s="6" t="str">
         <f aca="false">IF(Sheet1!C125="","",Sheet1!C125)</f>
         <v/>
       </c>
-      <c r="D125" s="5" t="str">
+      <c r="D125" s="6" t="str">
         <f aca="false">IF(Sheet1!D125="","",Sheet1!D125)</f>
         <v/>
       </c>
-      <c r="E125" s="5" t="str">
+      <c r="E125" s="6" t="str">
         <f aca="false">IF(Sheet1!E125="","",Sheet1!E125)</f>
         <v/>
       </c>
-      <c r="F125" s="5" t="str">
+      <c r="F125" s="6" t="str">
         <f aca="false">IF(Sheet1!F125="","",Sheet1!F125)</f>
         <v/>
       </c>
@@ -5294,30 +5298,30 @@
         <f aca="false">LEFT(F125,1)</f>
         <v/>
       </c>
-      <c r="I125" s="12"/>
-    </row>
-    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I125" s="13"/>
+    </row>
+    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="str">
         <f aca="false">IF(Sheet1!A126="","",Sheet1!A126)</f>
         <v/>
       </c>
-      <c r="B126" s="5" t="str">
+      <c r="B126" s="6" t="str">
         <f aca="false">IF(Sheet1!B126="","",Sheet1!B126)</f>
         <v/>
       </c>
-      <c r="C126" s="5" t="str">
+      <c r="C126" s="6" t="str">
         <f aca="false">IF(Sheet1!C126="","",Sheet1!C126)</f>
         <v/>
       </c>
-      <c r="D126" s="5" t="str">
+      <c r="D126" s="6" t="str">
         <f aca="false">IF(Sheet1!D126="","",Sheet1!D126)</f>
         <v/>
       </c>
-      <c r="E126" s="5" t="str">
+      <c r="E126" s="6" t="str">
         <f aca="false">IF(Sheet1!E126="","",Sheet1!E126)</f>
         <v/>
       </c>
-      <c r="F126" s="5" t="str">
+      <c r="F126" s="6" t="str">
         <f aca="false">IF(Sheet1!F126="","",Sheet1!F126)</f>
         <v/>
       </c>
@@ -5325,30 +5329,30 @@
         <f aca="false">LEFT(F126,1)</f>
         <v/>
       </c>
-      <c r="I126" s="12"/>
-    </row>
-    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I126" s="13"/>
+    </row>
+    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="str">
         <f aca="false">IF(Sheet1!A127="","",Sheet1!A127)</f>
         <v/>
       </c>
-      <c r="B127" s="5" t="str">
+      <c r="B127" s="6" t="str">
         <f aca="false">IF(Sheet1!B127="","",Sheet1!B127)</f>
         <v/>
       </c>
-      <c r="C127" s="5" t="str">
+      <c r="C127" s="6" t="str">
         <f aca="false">IF(Sheet1!C127="","",Sheet1!C127)</f>
         <v/>
       </c>
-      <c r="D127" s="5" t="str">
+      <c r="D127" s="6" t="str">
         <f aca="false">IF(Sheet1!D127="","",Sheet1!D127)</f>
         <v/>
       </c>
-      <c r="E127" s="5" t="str">
+      <c r="E127" s="6" t="str">
         <f aca="false">IF(Sheet1!E127="","",Sheet1!E127)</f>
         <v/>
       </c>
-      <c r="F127" s="5" t="str">
+      <c r="F127" s="6" t="str">
         <f aca="false">IF(Sheet1!F127="","",Sheet1!F127)</f>
         <v/>
       </c>
@@ -5356,30 +5360,30 @@
         <f aca="false">LEFT(F127,1)</f>
         <v/>
       </c>
-      <c r="I127" s="12"/>
-    </row>
-    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I127" s="13"/>
+    </row>
+    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="str">
         <f aca="false">IF(Sheet1!A128="","",Sheet1!A128)</f>
         <v/>
       </c>
-      <c r="B128" s="5" t="str">
+      <c r="B128" s="6" t="str">
         <f aca="false">IF(Sheet1!B128="","",Sheet1!B128)</f>
         <v/>
       </c>
-      <c r="C128" s="5" t="str">
+      <c r="C128" s="6" t="str">
         <f aca="false">IF(Sheet1!C128="","",Sheet1!C128)</f>
         <v/>
       </c>
-      <c r="D128" s="5" t="str">
+      <c r="D128" s="6" t="str">
         <f aca="false">IF(Sheet1!D128="","",Sheet1!D128)</f>
         <v/>
       </c>
-      <c r="E128" s="5" t="str">
+      <c r="E128" s="6" t="str">
         <f aca="false">IF(Sheet1!E128="","",Sheet1!E128)</f>
         <v/>
       </c>
-      <c r="F128" s="5" t="str">
+      <c r="F128" s="6" t="str">
         <f aca="false">IF(Sheet1!F128="","",Sheet1!F128)</f>
         <v/>
       </c>
@@ -5387,30 +5391,30 @@
         <f aca="false">LEFT(F128,1)</f>
         <v/>
       </c>
-      <c r="I128" s="12"/>
-    </row>
-    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I128" s="13"/>
+    </row>
+    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="str">
         <f aca="false">IF(Sheet1!A129="","",Sheet1!A129)</f>
         <v/>
       </c>
-      <c r="B129" s="5" t="str">
+      <c r="B129" s="6" t="str">
         <f aca="false">IF(Sheet1!B129="","",Sheet1!B129)</f>
         <v/>
       </c>
-      <c r="C129" s="5" t="str">
+      <c r="C129" s="6" t="str">
         <f aca="false">IF(Sheet1!C129="","",Sheet1!C129)</f>
         <v/>
       </c>
-      <c r="D129" s="5" t="str">
+      <c r="D129" s="6" t="str">
         <f aca="false">IF(Sheet1!D129="","",Sheet1!D129)</f>
         <v/>
       </c>
-      <c r="E129" s="5" t="str">
+      <c r="E129" s="6" t="str">
         <f aca="false">IF(Sheet1!E129="","",Sheet1!E129)</f>
         <v/>
       </c>
-      <c r="F129" s="5" t="str">
+      <c r="F129" s="6" t="str">
         <f aca="false">IF(Sheet1!F129="","",Sheet1!F129)</f>
         <v/>
       </c>
@@ -5418,30 +5422,30 @@
         <f aca="false">LEFT(F129,1)</f>
         <v/>
       </c>
-      <c r="I129" s="12"/>
-    </row>
-    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I129" s="13"/>
+    </row>
+    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="str">
         <f aca="false">IF(Sheet1!A130="","",Sheet1!A130)</f>
         <v/>
       </c>
-      <c r="B130" s="5" t="str">
+      <c r="B130" s="6" t="str">
         <f aca="false">IF(Sheet1!B130="","",Sheet1!B130)</f>
         <v/>
       </c>
-      <c r="C130" s="5" t="str">
+      <c r="C130" s="6" t="str">
         <f aca="false">IF(Sheet1!C130="","",Sheet1!C130)</f>
         <v/>
       </c>
-      <c r="D130" s="5" t="str">
+      <c r="D130" s="6" t="str">
         <f aca="false">IF(Sheet1!D130="","",Sheet1!D130)</f>
         <v/>
       </c>
-      <c r="E130" s="5" t="str">
+      <c r="E130" s="6" t="str">
         <f aca="false">IF(Sheet1!E130="","",Sheet1!E130)</f>
         <v/>
       </c>
-      <c r="F130" s="5" t="str">
+      <c r="F130" s="6" t="str">
         <f aca="false">IF(Sheet1!F130="","",Sheet1!F130)</f>
         <v/>
       </c>
@@ -5449,30 +5453,30 @@
         <f aca="false">LEFT(F130,1)</f>
         <v/>
       </c>
-      <c r="I130" s="12"/>
-    </row>
-    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I130" s="13"/>
+    </row>
+    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="str">
         <f aca="false">IF(Sheet1!A131="","",Sheet1!A131)</f>
         <v/>
       </c>
-      <c r="B131" s="5" t="str">
+      <c r="B131" s="6" t="str">
         <f aca="false">IF(Sheet1!B131="","",Sheet1!B131)</f>
         <v/>
       </c>
-      <c r="C131" s="5" t="str">
+      <c r="C131" s="6" t="str">
         <f aca="false">IF(Sheet1!C131="","",Sheet1!C131)</f>
         <v/>
       </c>
-      <c r="D131" s="5" t="str">
+      <c r="D131" s="6" t="str">
         <f aca="false">IF(Sheet1!D131="","",Sheet1!D131)</f>
         <v/>
       </c>
-      <c r="E131" s="5" t="str">
+      <c r="E131" s="6" t="str">
         <f aca="false">IF(Sheet1!E131="","",Sheet1!E131)</f>
         <v/>
       </c>
-      <c r="F131" s="5" t="str">
+      <c r="F131" s="6" t="str">
         <f aca="false">IF(Sheet1!F131="","",Sheet1!F131)</f>
         <v/>
       </c>
@@ -5480,30 +5484,30 @@
         <f aca="false">LEFT(F131,1)</f>
         <v/>
       </c>
-      <c r="I131" s="12"/>
-    </row>
-    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I131" s="13"/>
+    </row>
+    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="str">
         <f aca="false">IF(Sheet1!A132="","",Sheet1!A132)</f>
         <v/>
       </c>
-      <c r="B132" s="5" t="str">
+      <c r="B132" s="6" t="str">
         <f aca="false">IF(Sheet1!B132="","",Sheet1!B132)</f>
         <v/>
       </c>
-      <c r="C132" s="5" t="str">
+      <c r="C132" s="6" t="str">
         <f aca="false">IF(Sheet1!C132="","",Sheet1!C132)</f>
         <v/>
       </c>
-      <c r="D132" s="5" t="str">
+      <c r="D132" s="6" t="str">
         <f aca="false">IF(Sheet1!D132="","",Sheet1!D132)</f>
         <v/>
       </c>
-      <c r="E132" s="5" t="str">
+      <c r="E132" s="6" t="str">
         <f aca="false">IF(Sheet1!E132="","",Sheet1!E132)</f>
         <v/>
       </c>
-      <c r="F132" s="5" t="str">
+      <c r="F132" s="6" t="str">
         <f aca="false">IF(Sheet1!F132="","",Sheet1!F132)</f>
         <v/>
       </c>
@@ -5511,30 +5515,30 @@
         <f aca="false">LEFT(F132,1)</f>
         <v/>
       </c>
-      <c r="I132" s="12"/>
-    </row>
-    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="13"/>
+    </row>
+    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="str">
         <f aca="false">IF(Sheet1!A133="","",Sheet1!A133)</f>
         <v/>
       </c>
-      <c r="B133" s="5" t="str">
+      <c r="B133" s="6" t="str">
         <f aca="false">IF(Sheet1!B133="","",Sheet1!B133)</f>
         <v/>
       </c>
-      <c r="C133" s="5" t="str">
+      <c r="C133" s="6" t="str">
         <f aca="false">IF(Sheet1!C133="","",Sheet1!C133)</f>
         <v/>
       </c>
-      <c r="D133" s="5" t="str">
+      <c r="D133" s="6" t="str">
         <f aca="false">IF(Sheet1!D133="","",Sheet1!D133)</f>
         <v/>
       </c>
-      <c r="E133" s="5" t="str">
+      <c r="E133" s="6" t="str">
         <f aca="false">IF(Sheet1!E133="","",Sheet1!E133)</f>
         <v/>
       </c>
-      <c r="F133" s="5" t="str">
+      <c r="F133" s="6" t="str">
         <f aca="false">IF(Sheet1!F133="","",Sheet1!F133)</f>
         <v/>
       </c>
@@ -5542,30 +5546,30 @@
         <f aca="false">LEFT(F133,1)</f>
         <v/>
       </c>
-      <c r="I133" s="12"/>
-    </row>
-    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I133" s="13"/>
+    </row>
+    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="str">
         <f aca="false">IF(Sheet1!A134="","",Sheet1!A134)</f>
         <v/>
       </c>
-      <c r="B134" s="5" t="str">
+      <c r="B134" s="6" t="str">
         <f aca="false">IF(Sheet1!B134="","",Sheet1!B134)</f>
         <v/>
       </c>
-      <c r="C134" s="5" t="str">
+      <c r="C134" s="6" t="str">
         <f aca="false">IF(Sheet1!C134="","",Sheet1!C134)</f>
         <v/>
       </c>
-      <c r="D134" s="5" t="str">
+      <c r="D134" s="6" t="str">
         <f aca="false">IF(Sheet1!D134="","",Sheet1!D134)</f>
         <v/>
       </c>
-      <c r="E134" s="5" t="str">
+      <c r="E134" s="6" t="str">
         <f aca="false">IF(Sheet1!E134="","",Sheet1!E134)</f>
         <v/>
       </c>
-      <c r="F134" s="5" t="str">
+      <c r="F134" s="6" t="str">
         <f aca="false">IF(Sheet1!F134="","",Sheet1!F134)</f>
         <v/>
       </c>
@@ -5573,30 +5577,30 @@
         <f aca="false">LEFT(F134,1)</f>
         <v/>
       </c>
-      <c r="I134" s="12"/>
-    </row>
-    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I134" s="13"/>
+    </row>
+    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="str">
         <f aca="false">IF(Sheet1!A135="","",Sheet1!A135)</f>
         <v/>
       </c>
-      <c r="B135" s="5" t="str">
+      <c r="B135" s="6" t="str">
         <f aca="false">IF(Sheet1!B135="","",Sheet1!B135)</f>
         <v/>
       </c>
-      <c r="C135" s="5" t="str">
+      <c r="C135" s="6" t="str">
         <f aca="false">IF(Sheet1!C135="","",Sheet1!C135)</f>
         <v/>
       </c>
-      <c r="D135" s="5" t="str">
+      <c r="D135" s="6" t="str">
         <f aca="false">IF(Sheet1!D135="","",Sheet1!D135)</f>
         <v/>
       </c>
-      <c r="E135" s="5" t="str">
+      <c r="E135" s="6" t="str">
         <f aca="false">IF(Sheet1!E135="","",Sheet1!E135)</f>
         <v/>
       </c>
-      <c r="F135" s="5" t="str">
+      <c r="F135" s="6" t="str">
         <f aca="false">IF(Sheet1!F135="","",Sheet1!F135)</f>
         <v/>
       </c>
@@ -5604,30 +5608,30 @@
         <f aca="false">LEFT(F135,1)</f>
         <v/>
       </c>
-      <c r="I135" s="12"/>
-    </row>
-    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I135" s="13"/>
+    </row>
+    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="str">
         <f aca="false">IF(Sheet1!A136="","",Sheet1!A136)</f>
         <v/>
       </c>
-      <c r="B136" s="5" t="str">
+      <c r="B136" s="6" t="str">
         <f aca="false">IF(Sheet1!B136="","",Sheet1!B136)</f>
         <v/>
       </c>
-      <c r="C136" s="5" t="str">
+      <c r="C136" s="6" t="str">
         <f aca="false">IF(Sheet1!C136="","",Sheet1!C136)</f>
         <v/>
       </c>
-      <c r="D136" s="5" t="str">
+      <c r="D136" s="6" t="str">
         <f aca="false">IF(Sheet1!D136="","",Sheet1!D136)</f>
         <v/>
       </c>
-      <c r="E136" s="5" t="str">
+      <c r="E136" s="6" t="str">
         <f aca="false">IF(Sheet1!E136="","",Sheet1!E136)</f>
         <v/>
       </c>
-      <c r="F136" s="5" t="str">
+      <c r="F136" s="6" t="str">
         <f aca="false">IF(Sheet1!F136="","",Sheet1!F136)</f>
         <v/>
       </c>
@@ -5635,30 +5639,30 @@
         <f aca="false">LEFT(F136,1)</f>
         <v/>
       </c>
-      <c r="I136" s="12"/>
-    </row>
-    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I136" s="13"/>
+    </row>
+    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="str">
         <f aca="false">IF(Sheet1!A137="","",Sheet1!A137)</f>
         <v/>
       </c>
-      <c r="B137" s="5" t="str">
+      <c r="B137" s="6" t="str">
         <f aca="false">IF(Sheet1!B137="","",Sheet1!B137)</f>
         <v/>
       </c>
-      <c r="C137" s="5" t="str">
+      <c r="C137" s="6" t="str">
         <f aca="false">IF(Sheet1!C137="","",Sheet1!C137)</f>
         <v/>
       </c>
-      <c r="D137" s="5" t="str">
+      <c r="D137" s="6" t="str">
         <f aca="false">IF(Sheet1!D137="","",Sheet1!D137)</f>
         <v/>
       </c>
-      <c r="E137" s="5" t="str">
+      <c r="E137" s="6" t="str">
         <f aca="false">IF(Sheet1!E137="","",Sheet1!E137)</f>
         <v/>
       </c>
-      <c r="F137" s="5" t="str">
+      <c r="F137" s="6" t="str">
         <f aca="false">IF(Sheet1!F137="","",Sheet1!F137)</f>
         <v/>
       </c>
@@ -5666,30 +5670,30 @@
         <f aca="false">LEFT(F137,1)</f>
         <v/>
       </c>
-      <c r="I137" s="12"/>
-    </row>
-    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I137" s="13"/>
+    </row>
+    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="str">
         <f aca="false">IF(Sheet1!A138="","",Sheet1!A138)</f>
         <v/>
       </c>
-      <c r="B138" s="5" t="str">
+      <c r="B138" s="6" t="str">
         <f aca="false">IF(Sheet1!B138="","",Sheet1!B138)</f>
         <v/>
       </c>
-      <c r="C138" s="5" t="str">
+      <c r="C138" s="6" t="str">
         <f aca="false">IF(Sheet1!C138="","",Sheet1!C138)</f>
         <v/>
       </c>
-      <c r="D138" s="5" t="str">
+      <c r="D138" s="6" t="str">
         <f aca="false">IF(Sheet1!D138="","",Sheet1!D138)</f>
         <v/>
       </c>
-      <c r="E138" s="5" t="str">
+      <c r="E138" s="6" t="str">
         <f aca="false">IF(Sheet1!E138="","",Sheet1!E138)</f>
         <v/>
       </c>
-      <c r="F138" s="5" t="str">
+      <c r="F138" s="6" t="str">
         <f aca="false">IF(Sheet1!F138="","",Sheet1!F138)</f>
         <v/>
       </c>
@@ -5697,30 +5701,30 @@
         <f aca="false">LEFT(F138,1)</f>
         <v/>
       </c>
-      <c r="I138" s="12"/>
-    </row>
-    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I138" s="13"/>
+    </row>
+    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="str">
         <f aca="false">IF(Sheet1!A139="","",Sheet1!A139)</f>
         <v/>
       </c>
-      <c r="B139" s="5" t="str">
+      <c r="B139" s="6" t="str">
         <f aca="false">IF(Sheet1!B139="","",Sheet1!B139)</f>
         <v/>
       </c>
-      <c r="C139" s="5" t="str">
+      <c r="C139" s="6" t="str">
         <f aca="false">IF(Sheet1!C139="","",Sheet1!C139)</f>
         <v/>
       </c>
-      <c r="D139" s="5" t="str">
+      <c r="D139" s="6" t="str">
         <f aca="false">IF(Sheet1!D139="","",Sheet1!D139)</f>
         <v/>
       </c>
-      <c r="E139" s="5" t="str">
+      <c r="E139" s="6" t="str">
         <f aca="false">IF(Sheet1!E139="","",Sheet1!E139)</f>
         <v/>
       </c>
-      <c r="F139" s="5" t="str">
+      <c r="F139" s="6" t="str">
         <f aca="false">IF(Sheet1!F139="","",Sheet1!F139)</f>
         <v/>
       </c>
@@ -5728,30 +5732,30 @@
         <f aca="false">LEFT(F139,1)</f>
         <v/>
       </c>
-      <c r="I139" s="12"/>
-    </row>
-    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I139" s="13"/>
+    </row>
+    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="str">
         <f aca="false">IF(Sheet1!A140="","",Sheet1!A140)</f>
         <v/>
       </c>
-      <c r="B140" s="5" t="str">
+      <c r="B140" s="6" t="str">
         <f aca="false">IF(Sheet1!B140="","",Sheet1!B140)</f>
         <v/>
       </c>
-      <c r="C140" s="5" t="str">
+      <c r="C140" s="6" t="str">
         <f aca="false">IF(Sheet1!C140="","",Sheet1!C140)</f>
         <v/>
       </c>
-      <c r="D140" s="5" t="str">
+      <c r="D140" s="6" t="str">
         <f aca="false">IF(Sheet1!D140="","",Sheet1!D140)</f>
         <v/>
       </c>
-      <c r="E140" s="5" t="str">
+      <c r="E140" s="6" t="str">
         <f aca="false">IF(Sheet1!E140="","",Sheet1!E140)</f>
         <v/>
       </c>
-      <c r="F140" s="5" t="str">
+      <c r="F140" s="6" t="str">
         <f aca="false">IF(Sheet1!F140="","",Sheet1!F140)</f>
         <v/>
       </c>
@@ -5759,7 +5763,7 @@
         <f aca="false">LEFT(F140,1)</f>
         <v/>
       </c>
-      <c r="I140" s="12"/>
+      <c r="I140" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
